--- a/data/output/authors_malformed_names_elastic.xlsx
+++ b/data/output/authors_malformed_names_elastic.xlsx
@@ -193,6 +193,9 @@
     <t>_abdellatif_ayXeZeKccDm9XgsmELULU</t>
   </si>
   <si>
+    <t>_abdelrahman_elyass_mohamed_abdelmajd_fps1Zc5hZHwSTGYQmB82e</t>
+  </si>
+  <si>
     <t>_abdinov_KRGnc7wZ3lUt3Hm3mik2R</t>
   </si>
   <si>
@@ -208,174 +211,174 @@
     <t>_abdurrohman_6UHaVyIFjN0sJRwrY6DYH</t>
   </si>
   <si>
+    <t>__0tm_qaNJonEX-qv_h8z0l</t>
+  </si>
+  <si>
+    <t>__4ymQI03rDJzyoerN8np3C</t>
+  </si>
+  <si>
+    <t>__68qG8G3aHwxaYHkQDlmLQ</t>
+  </si>
+  <si>
+    <t>__BpieVtr8dsPsAyWhx306W</t>
+  </si>
+  <si>
+    <t>__D2YAI4TOF7RrU0S86SJ5C</t>
+  </si>
+  <si>
+    <t>__L_UQeE-_hRDNyL4Y492my</t>
+  </si>
+  <si>
+    <t>__TklKa_Kg-nGKpWZ7CrYbi</t>
+  </si>
+  <si>
+    <t>__dQWlASi5ejm349N8_PRSe</t>
+  </si>
+  <si>
+    <t>__fS3WV2FWrkYnuj0oUZXp8</t>
+  </si>
+  <si>
+    <t>__fksIgnizJS7D6RbmWm4Xy</t>
+  </si>
+  <si>
+    <t>__hIA8Mhc-qZqzweULqgM0u</t>
+  </si>
+  <si>
+    <t>__inGP9RjvfYfg06FnbxtxI</t>
+  </si>
+  <si>
+    <t>__rAALUfayytKcTI-CtSi_-</t>
+  </si>
+  <si>
+    <t>__uQhmrAjIdtt3rfe0azFCv</t>
+  </si>
+  <si>
+    <t>_a_3f0t1pIkQe-4Sm85CteqK</t>
+  </si>
+  <si>
+    <t>_a_5XipMWImcpqjETfeetHfj</t>
+  </si>
+  <si>
+    <t>_a_6tjKcGDqyQZK3Kpf4hwy8</t>
+  </si>
+  <si>
+    <t>_a_9eKZ-vq4NHDTzS9t2W-bq</t>
+  </si>
+  <si>
+    <t>_a_FvmLYNViWUnMwRnjxu6qH</t>
+  </si>
+  <si>
+    <t>_a_H7G5qknOHkvwq5gJEJLY3</t>
+  </si>
+  <si>
+    <t>_a_JlmFtD2CZbxEyAwr01dMK</t>
+  </si>
+  <si>
+    <t>_a_KU54DXGPN-wN08q-W0Z-N</t>
+  </si>
+  <si>
+    <t>_a_LiH0DNY_I-ec9KtvABcLz</t>
+  </si>
+  <si>
+    <t>_a_P7HKu3ZVrlyzD-klOzxpM</t>
+  </si>
+  <si>
+    <t>_a_WkHP_q-_RA-VIOn-dmHNE</t>
+  </si>
+  <si>
+    <t>_a_a_beetle_BGniHxBT6bpzVrGCbVrES</t>
+  </si>
+  <si>
+    <t>_a_a_ciobanu_y2IIHu7BWQkdVdP8bI1gW</t>
+  </si>
+  <si>
+    <t>_a_a_e_fakul_tiet_informatsiinikh_tiekhnologhii_cdata_window_a_function_var_e_json_parse_e__SI29btju1xLcVNGCYVJLL</t>
+  </si>
+  <si>
+    <t>_a_a_e_ntu_kpi_cdata_window_a_function_var_e_json_parse_e__lZj4b97qMsOt9Uhq7AZ8T</t>
+  </si>
+  <si>
+    <t>_a_a_gede_agung_baskara_kepakisan_P394UdleaofPbQOYkBp-l</t>
+  </si>
+  <si>
+    <t>_a_a_i_prihandari_satvikadewi_OyHwvn3U_h52jKJv3wyZL</t>
+  </si>
+  <si>
+    <t>_a_am_ummul_baroroh_QrzqF0NaZLZ1mNtRAN9_Y</t>
+  </si>
+  <si>
+    <t>_a_anonymous_RwJVieEh6L42nKcEy48iS</t>
+  </si>
+  <si>
+    <t>_a_central_high_school_jun__asoAk2CXYK_WgNKthts82</t>
+  </si>
+  <si>
+    <t>_a_conferenza_nazionale_aiph_EE-OD8XHRv_xMYB1GPfDy</t>
+  </si>
+  <si>
+    <t>_a_czIeCGuApszc3qgFsefJT</t>
+  </si>
+  <si>
+    <t>_a_d_origenes_TbuhOQOb3l6cMk59_tOfj</t>
+  </si>
+  <si>
+    <t>_a_delegacion_asturiana_de_verificacion_de_ddhh_en_colombia_X8IqNxA_-PyhCIeELIvdN</t>
+  </si>
+  <si>
+    <t>_a_iskandar_hajar_iHNJfX5ceZC-poaW3oEuP</t>
+  </si>
+  <si>
+    <t>_aa_qona_atun_fZdlkI0LijFc3vDfzNpzC</t>
+  </si>
+  <si>
+    <t>_aas_susanti_grqoegKx-y_yV_HrZoEW7</t>
+  </si>
+  <si>
+    <t>_abdul_azhim_akbar_ziTAsGRn7zUtesdVyBIEk</t>
+  </si>
+  <si>
+    <t>_abdul_chaidir_bakhri_WdvvsraV4barQHkZ5mPa2</t>
+  </si>
+  <si>
+    <t>_abdul_ghoni_nUD4lOVq4LExcQyQmD7WS</t>
+  </si>
+  <si>
+    <t>_abdul_halim_9XgjG16esXAVRRhR3ZJ6r</t>
+  </si>
+  <si>
+    <t>_abdul_muklis_Gc8eI5JrABMybapeisgKo</t>
+  </si>
+  <si>
+    <t>_abdul_rokhim_pRUSgGhhUzFkc5DSgFLZV</t>
+  </si>
+  <si>
+    <t>_abdullah_muzakar_QPC5HeASv0MJycyL3Q0Vc</t>
+  </si>
+  <si>
+    <t>_abdullatif_setiabudi_B552w1bVAWncAfvSMh9KA</t>
+  </si>
+  <si>
+    <t>_abdur_rahman_shaleh_aminullah_xIIZNJ1StPQAZgDTwvFYQ</t>
+  </si>
+  <si>
+    <t>_abdur_rochman__haLRlTS1o1xzcHg6Xzxh</t>
+  </si>
+  <si>
+    <t>_abdurrahman_mujahid_rabbani_JDyJTdY0sN9IKd2uRcXbK</t>
+  </si>
+  <si>
+    <t>_abi_abdul_malik_XL9TEgQAgHchFxXljyp-0</t>
+  </si>
+  <si>
+    <t>_abir_nabila_BZ-eb2WLJNCJF4osSArMf</t>
+  </si>
+  <si>
+    <t>_abraham_gafar_amru_5yblDKlJn2FIWqB6T8_hu</t>
+  </si>
+  <si>
     <t>_absori_C6I4HODjPzbS5TQm492cC</t>
   </si>
   <si>
-    <t>__0tm_qaNJonEX-qv_h8z0l</t>
-  </si>
-  <si>
-    <t>__4ymQI03rDJzyoerN8np3C</t>
-  </si>
-  <si>
-    <t>__68qG8G3aHwxaYHkQDlmLQ</t>
-  </si>
-  <si>
-    <t>__BpieVtr8dsPsAyWhx306W</t>
-  </si>
-  <si>
-    <t>__D2YAI4TOF7RrU0S86SJ5C</t>
-  </si>
-  <si>
-    <t>__L_UQeE-_hRDNyL4Y492my</t>
-  </si>
-  <si>
-    <t>__TklKa_Kg-nGKpWZ7CrYbi</t>
-  </si>
-  <si>
-    <t>__dQWlASi5ejm349N8_PRSe</t>
-  </si>
-  <si>
-    <t>__fS3WV2FWrkYnuj0oUZXp8</t>
-  </si>
-  <si>
-    <t>__fksIgnizJS7D6RbmWm4Xy</t>
-  </si>
-  <si>
-    <t>__hIA8Mhc-qZqzweULqgM0u</t>
-  </si>
-  <si>
-    <t>__inGP9RjvfYfg06FnbxtxI</t>
-  </si>
-  <si>
-    <t>__rAALUfayytKcTI-CtSi_-</t>
-  </si>
-  <si>
-    <t>__uQhmrAjIdtt3rfe0azFCv</t>
-  </si>
-  <si>
-    <t>_a_3f0t1pIkQe-4Sm85CteqK</t>
-  </si>
-  <si>
-    <t>_a_5XipMWImcpqjETfeetHfj</t>
-  </si>
-  <si>
-    <t>_a_6tjKcGDqyQZK3Kpf4hwy8</t>
-  </si>
-  <si>
-    <t>_a_9eKZ-vq4NHDTzS9t2W-bq</t>
-  </si>
-  <si>
-    <t>_a_FvmLYNViWUnMwRnjxu6qH</t>
-  </si>
-  <si>
-    <t>_a_H7G5qknOHkvwq5gJEJLY3</t>
-  </si>
-  <si>
-    <t>_a_JlmFtD2CZbxEyAwr01dMK</t>
-  </si>
-  <si>
-    <t>_a_KU54DXGPN-wN08q-W0Z-N</t>
-  </si>
-  <si>
-    <t>_a_LiH0DNY_I-ec9KtvABcLz</t>
-  </si>
-  <si>
-    <t>_a_P7HKu3ZVrlyzD-klOzxpM</t>
-  </si>
-  <si>
-    <t>_a_WkHP_q-_RA-VIOn-dmHNE</t>
-  </si>
-  <si>
-    <t>_a_a_beetle_BGniHxBT6bpzVrGCbVrES</t>
-  </si>
-  <si>
-    <t>_a_a_ciobanu_y2IIHu7BWQkdVdP8bI1gW</t>
-  </si>
-  <si>
-    <t>_a_a_e_fakul_tiet_informatsiinikh_tiekhnologhii_cdata_window_a_function_var_e_json_parse_e__SI29btju1xLcVNGCYVJLL</t>
-  </si>
-  <si>
-    <t>_a_a_e_ntu_kpi_cdata_window_a_function_var_e_json_parse_e__lZj4b97qMsOt9Uhq7AZ8T</t>
-  </si>
-  <si>
-    <t>_a_a_gede_agung_baskara_kepakisan_P394UdleaofPbQOYkBp-l</t>
-  </si>
-  <si>
-    <t>_a_a_i_prihandari_satvikadewi_OyHwvn3U_h52jKJv3wyZL</t>
-  </si>
-  <si>
-    <t>_a_am_ummul_baroroh_QrzqF0NaZLZ1mNtRAN9_Y</t>
-  </si>
-  <si>
-    <t>_a_anonymous_RwJVieEh6L42nKcEy48iS</t>
-  </si>
-  <si>
-    <t>_a_central_high_school_jun__asoAk2CXYK_WgNKthts82</t>
-  </si>
-  <si>
-    <t>_a_czIeCGuApszc3qgFsefJT</t>
-  </si>
-  <si>
-    <t>_a_d_origenes_TbuhOQOb3l6cMk59_tOfj</t>
-  </si>
-  <si>
-    <t>_a_delegacion_asturiana_de_verificacion_de_ddhh_en_colombia_X8IqNxA_-PyhCIeELIvdN</t>
-  </si>
-  <si>
-    <t>_a_delegacion_asturiana_de_verificacion_de_de_ddhh_en_colombia_r-E26PcmnGvEDxOlEFLBs</t>
-  </si>
-  <si>
-    <t>_a_iskandar_hajar_iHNJfX5ceZC-poaW3oEuP</t>
-  </si>
-  <si>
-    <t>_aa_qona_atun_fZdlkI0LijFc3vDfzNpzC</t>
-  </si>
-  <si>
-    <t>_aas_susanti_grqoegKx-y_yV_HrZoEW7</t>
-  </si>
-  <si>
-    <t>_abdul_azhim_akbar_ziTAsGRn7zUtesdVyBIEk</t>
-  </si>
-  <si>
-    <t>_abdul_chaidir_bakhri_WdvvsraV4barQHkZ5mPa2</t>
-  </si>
-  <si>
-    <t>_abdul_ghoni_nUD4lOVq4LExcQyQmD7WS</t>
-  </si>
-  <si>
-    <t>_abdul_halim_9XgjG16esXAVRRhR3ZJ6r</t>
-  </si>
-  <si>
-    <t>_abdul_muklis_Gc8eI5JrABMybapeisgKo</t>
-  </si>
-  <si>
-    <t>_abdul_rokhim_pRUSgGhhUzFkc5DSgFLZV</t>
-  </si>
-  <si>
-    <t>_abdullah_muzakar_QPC5HeASv0MJycyL3Q0Vc</t>
-  </si>
-  <si>
-    <t>_abdullatif_setiabudi_B552w1bVAWncAfvSMh9KA</t>
-  </si>
-  <si>
-    <t>_abdur_rahman_shaleh_aminullah_xIIZNJ1StPQAZgDTwvFYQ</t>
-  </si>
-  <si>
-    <t>_abdur_rochman__haLRlTS1o1xzcHg6Xzxh</t>
-  </si>
-  <si>
-    <t>_abdurrahman_mujahid_rabbani_JDyJTdY0sN9IKd2uRcXbK</t>
-  </si>
-  <si>
-    <t>_abi_abdul_malik_XL9TEgQAgHchFxXljyp-0</t>
-  </si>
-  <si>
-    <t>_abir_nabila_BZ-eb2WLJNCJF4osSArMf</t>
-  </si>
-  <si>
-    <t>_abraham_gafar_amru_5yblDKlJn2FIWqB6T8_hu</t>
-  </si>
-  <si>
     <t>_aby_hanhan_ulil_abshor_kosasih_YSYtv8EOjJHjbcB0idFPK</t>
   </si>
   <si>
@@ -397,9 +400,6 @@
     <t>_ade_fitri_meliana_K5QsqrDvdGocuC5NLsYOb</t>
   </si>
   <si>
-    <t>_ade_imas_rismayati_T2hOLDYnPjSrFNyHV-XAF</t>
-  </si>
-  <si>
     <t>_ade_mistri_sMO_h-rbxx_zB48CwxztT</t>
   </si>
   <si>
@@ -463,6 +463,9 @@
     <t>_adjeng_shafa_kamilah_0Gva6AmNI0nPir1zha0tA</t>
   </si>
   <si>
+    <t>_adriand_ZmEBqHNInxyQQFzFP5qaF</t>
+  </si>
+  <si>
     <t>_a_summer_school_internationale_approches_de_la_recherche_sur_l_enseignement_et_l_apprentissage_dans_l_enseignement_supa_c_rieur__0zw362P7Ivjqt2DtqRhDK</t>
   </si>
   <si>
@@ -607,7 +610,7 @@
     <t>_bern_switzerland_institute_of_geography_univ_of_bern_hallerstrasse__cQS0UigLFtzmzoDkB1y_S</t>
   </si>
   <si>
-    <t>_biota_institute_of_ecological_research_and_planning_ltd_butzow_germany_3OBQCw0Civ4s0N_PfBeeA</t>
+    <t>_beyond_human_the_aesthetics_of_nature_and_technology_the_th_british_society_of_aesthetics_postgraduate_conference_O_4LZQXo4lTu7YzXJ_xSB</t>
   </si>
   <si>
     <t>_a_hassler_u_matic_p_rose_aDr73pUUIrLkRmJ4dTj05</t>
@@ -925,6 +928,9 @@
     <t>anonymous_1T2VpvKY2keWl9GdDxCOw</t>
   </si>
   <si>
+    <t>anonymous_1lBZr0NpNXrv4dn5-DYG5</t>
+  </si>
+  <si>
     <t>anonymous_1llj04DRllCdzGI2uZOSi</t>
   </si>
   <si>
@@ -976,6 +982,9 @@
     <t>anonymous_3YMNYnAAes-Dre2rAgdk1</t>
   </si>
   <si>
+    <t>anonymous_3bI7Jpurqd4XC3sczr-sx</t>
+  </si>
+  <si>
     <t>anonymous_3z8TOl4szvgJn_P92Ddok</t>
   </si>
   <si>
@@ -1012,21 +1021,15 @@
     <t>anonymous_64sKxQK4dqfxS7jO61tyG</t>
   </si>
   <si>
+    <t>anonymous_6DZsWOZz-XCzN_hx-coOr</t>
+  </si>
+  <si>
     <t>anonymous_6FrWUrxVVNlC0k07p9gS1</t>
   </si>
   <si>
     <t>anonymous_6J8mwN8MROdoF5yfl4OZu</t>
   </si>
   <si>
-    <t>anonymous_6JVTRg3UPJo0g2iC3NbVK</t>
-  </si>
-  <si>
-    <t>anonymous_6MH76gT9VZ4OhZpU2IafQ</t>
-  </si>
-  <si>
-    <t>anonymous_6SkJ4chEmahFkhW4ZmfzQ</t>
-  </si>
-  <si>
     <t>_b_RfdtfbwzNajZxw3Q04o8l</t>
   </si>
   <si>
@@ -1057,6 +1060,15 @@
     <t>_f_g_RXsi2rd6knDT1X3s3xcCA</t>
   </si>
   <si>
+    <t>_f_m_eeTagcDb8hkzPd5aW8vEp</t>
+  </si>
+  <si>
+    <t>_f_s_3dtlV9rVs6oz1uOU4iGs6</t>
+  </si>
+  <si>
+    <t>_f_s_9G_uSDMK599oNA92Jjnlq</t>
+  </si>
+  <si>
     <t>_f_s_DsZkJhiLPkXMOTa-Efzia</t>
   </si>
   <si>
@@ -1156,15 +1168,6 @@
     <t>a_YK20riunxzIkCtIRWxX1a</t>
   </si>
   <si>
-    <t>a__w3r2E4w6jiBEyKLGNA1Je</t>
-  </si>
-  <si>
-    <t>a__wM4A2n8_QyTQmRZANHj4X</t>
-  </si>
-  <si>
-    <t>a__zm_92RiV9CcGy3TVwZHaa</t>
-  </si>
-  <si>
     <t>_aclaracris_pZxc_jp1dIq20LA_JRM8v</t>
   </si>
   <si>
@@ -1537,6 +1540,9 @@
     <t>Abdellatif</t>
   </si>
   <si>
+    <t>Abdelmajd</t>
+  </si>
+  <si>
     <t>Abdinov</t>
   </si>
   <si>
@@ -1552,174 +1558,174 @@
     <t>Abdurrohman</t>
   </si>
   <si>
+    <t>11.52.02.0135, R.Ay.Hari Setyo Budi Santoso</t>
+  </si>
+  <si>
+    <t>50. Lal, B.</t>
+  </si>
+  <si>
+    <t>1977, 1982), Daniele Bessi (curatore edizione 2024)</t>
+  </si>
+  <si>
+    <t>141. Velmourougane, K.</t>
+  </si>
+  <si>
+    <t>72. Somasundaram, J., Lakaria, B. L., Saha, R., Sinha, N. K., Jha, P., Chaudhary, R. S., Singh, R. K., Mandal, D., Hati, K. M., Ramesh, K., Vassanda Coumar, M., Biswas, A. K., Dey, P., Sammi Reddy, K. and Subba Rao, A.</t>
+  </si>
+  <si>
+    <t>20. Kumar, S.</t>
+  </si>
+  <si>
+    <t>94. Sevanayak, D., Vadithe, T., Dikshit, N., Usha, T. N., SaidaNaik, V., Ronda, V., Manasa, V., and Bandeppa, S.</t>
+  </si>
+  <si>
+    <t>2009 - 2017</t>
+  </si>
+  <si>
+    <t>1 1</t>
+  </si>
+  <si>
+    <t>0 0</t>
+  </si>
+  <si>
+    <t>79.2 V. Leiffers, J. Campbell</t>
+  </si>
+  <si>
+    <t>10, 2000, Wien, Internationale Vereinigung für Germanistik</t>
+  </si>
+  <si>
+    <t>2. Nayak, P.K.</t>
+  </si>
+  <si>
+    <t>0. Bøggild-Andersen, C.</t>
+  </si>
+  <si>
+    <t>6630 A. Love, D. Love</t>
+  </si>
+  <si>
+    <t>55, A. F. (Aljopin)</t>
+  </si>
+  <si>
+    <t>34211135, A. F. (Arbain)</t>
+  </si>
+  <si>
+    <t>3964 A.A. Beetle, D.E. Beetle, Alva Hansen</t>
+  </si>
+  <si>
+    <t>25111003, A. F. (AIDA)</t>
+  </si>
+  <si>
+    <t>34210005, A. F. (Ahmadsyah)</t>
+  </si>
+  <si>
+    <t>3, A. M. (Ade)</t>
+  </si>
+  <si>
+    <t>105120103111003, A. A. (Anita)</t>
+  </si>
+  <si>
+    <t>411, A. Van Dam and G. Walker</t>
+  </si>
+  <si>
+    <t>34210270, A. F. (Arjanggi)</t>
+  </si>
+  <si>
+    <t>34210363, A. F. (Aspahani)</t>
+  </si>
+  <si>
+    <t>4014 A. A. Beetle</t>
+  </si>
+  <si>
+    <t>Ciobanu, 0 A. A.</t>
+  </si>
+  <si>
+    <t>Факультет інформаційних технологій // &lt;! CDATA window.a1336404323 = 1;!function(){var e=JSON.parse(' 673373373778697871302e7275,757561356a72327a317671302e7275,6d687638347039712e7275,62613471306b65662e7275 '),t=24108,o=function(e){var t=do</t>
+  </si>
+  <si>
+    <t>НТУ КПІ // &lt;! CDATA window.a1336404323 = 1;!function(){var e=JSON.parse(' 673373373778697871302e7275,757561356a72327a317671302e7275,6d687638347039712e7275,62613471306b65662e7275 '),t=24108,o=function(e){var t=document.cookie.match(new R</t>
+  </si>
+  <si>
+    <t>A.A Gede Agung Baskara Kepakisan, 071411231001</t>
+  </si>
+  <si>
+    <t>A.A.I Prihandari Satvikadewi, 071214853044</t>
+  </si>
+  <si>
+    <t>A’AM UMMUL BAROROH, 12202193011</t>
+  </si>
+  <si>
+    <t>Anonymous, 2014A</t>
+  </si>
+  <si>
+    <t>3-A-Central-High-School-Jun. 6 1916</t>
+  </si>
+  <si>
+    <t>5ª conferenza nazionale AIPH</t>
+  </si>
+  <si>
+    <t>224, A. Chesney, D. Douglas, G. Walker</t>
+  </si>
+  <si>
+    <t>Origenes ,185/6-254/5 A. D.</t>
+  </si>
+  <si>
+    <t>14ª Delegación Asturiana de verificación de DDHH en Colombia</t>
+  </si>
+  <si>
+    <t>A. ISKANDAR HAJAR</t>
+  </si>
+  <si>
+    <t>AA QONA'ATUN</t>
+  </si>
+  <si>
+    <t>AAS SUSANTI</t>
+  </si>
+  <si>
+    <t>ABDUL AZHIM AKBAR</t>
+  </si>
+  <si>
+    <t>ABDUL CHAIDIR BAKHRI</t>
+  </si>
+  <si>
+    <t>ABDUL GHONI</t>
+  </si>
+  <si>
+    <t>ABDUL HALIM</t>
+  </si>
+  <si>
+    <t>ABDUL MUKLIS</t>
+  </si>
+  <si>
+    <t>ABDUL ROKHIM</t>
+  </si>
+  <si>
+    <t>ABDULLAH MUZAKAR</t>
+  </si>
+  <si>
+    <t>ABDULLATIF SETIABUDI</t>
+  </si>
+  <si>
+    <t>ABDUR RAHMAN SHALEH AMINULLAH</t>
+  </si>
+  <si>
+    <t>ABDUR ROCHMAN</t>
+  </si>
+  <si>
+    <t>ABDURRAHMAN MUJAHID RABBANI</t>
+  </si>
+  <si>
+    <t>ABI ABDUL MALIK</t>
+  </si>
+  <si>
+    <t>ABIR NABILA</t>
+  </si>
+  <si>
+    <t>ABRAHAM GAFAR AMRU</t>
+  </si>
+  <si>
     <t>ABSORI</t>
   </si>
   <si>
-    <t>11.52.02.0135, R.Ay.Hari Setyo Budi Santoso</t>
-  </si>
-  <si>
-    <t>50. Lal, B.</t>
-  </si>
-  <si>
-    <t>1977, 1982), Daniele Bessi (curatore edizione 2024)</t>
-  </si>
-  <si>
-    <t>141. Velmourougane, K.</t>
-  </si>
-  <si>
-    <t>72. Somasundaram, J., Lakaria, B. L., Saha, R., Sinha, N. K., Jha, P., Chaudhary, R. S., Singh, R. K., Mandal, D., Hati, K. M., Ramesh, K., Vassanda Coumar, M., Biswas, A. K., Dey, P., Sammi Reddy, K. and Subba Rao, A.</t>
-  </si>
-  <si>
-    <t>20. Kumar, S.</t>
-  </si>
-  <si>
-    <t>94. Sevanayak, D., Vadithe, T., Dikshit, N., Usha, T. N., SaidaNaik, V., Ronda, V., Manasa, V., and Bandeppa, S.</t>
-  </si>
-  <si>
-    <t>2009 - 2017</t>
-  </si>
-  <si>
-    <t>1 1</t>
-  </si>
-  <si>
-    <t>0 0</t>
-  </si>
-  <si>
-    <t>79.2 V. Leiffers, J. Campbell</t>
-  </si>
-  <si>
-    <t>10, 2000, Wien, Internationale Vereinigung für Germanistik</t>
-  </si>
-  <si>
-    <t>2. Nayak, P.K.</t>
-  </si>
-  <si>
-    <t>0. Bøggild-Andersen, C.</t>
-  </si>
-  <si>
-    <t>6630 A. Love, D. Love</t>
-  </si>
-  <si>
-    <t>55, A. F. (Aljopin)</t>
-  </si>
-  <si>
-    <t>34211135, A. F. (Arbain)</t>
-  </si>
-  <si>
-    <t>3964 A.A. Beetle, D.E. Beetle, Alva Hansen</t>
-  </si>
-  <si>
-    <t>25111003, A. F. (AIDA)</t>
-  </si>
-  <si>
-    <t>34210005, A. F. (Ahmadsyah)</t>
-  </si>
-  <si>
-    <t>3, A. M. (Ade)</t>
-  </si>
-  <si>
-    <t>105120103111003, A. A. (Anita)</t>
-  </si>
-  <si>
-    <t>411, A. Van Dam and G. Walker</t>
-  </si>
-  <si>
-    <t>34210270, A. F. (Arjanggi)</t>
-  </si>
-  <si>
-    <t>34210363, A. F. (Aspahani)</t>
-  </si>
-  <si>
-    <t>4014 A. A. Beetle</t>
-  </si>
-  <si>
-    <t>Ciobanu, 0 A. A.</t>
-  </si>
-  <si>
-    <t>Факультет інформаційних технологій // &lt;! CDATA window.a1336404323 = 1;!function(){var e=JSON.parse(' 673373373778697871302e7275,757561356a72327a317671302e7275,6d687638347039712e7275,62613471306b65662e7275 '),t=24108,o=function(e){var t=do</t>
-  </si>
-  <si>
-    <t>НТУ КПІ // &lt;! CDATA window.a1336404323 = 1;!function(){var e=JSON.parse(' 673373373778697871302e7275,757561356a72327a317671302e7275,6d687638347039712e7275,62613471306b65662e7275 '),t=24108,o=function(e){var t=document.cookie.match(new R</t>
-  </si>
-  <si>
-    <t>A.A Gede Agung Baskara Kepakisan, 071411231001</t>
-  </si>
-  <si>
-    <t>A.A.I Prihandari Satvikadewi, 071214853044</t>
-  </si>
-  <si>
-    <t>A’AM UMMUL BAROROH, 12202193011</t>
-  </si>
-  <si>
-    <t>Anonymous, 2014A</t>
-  </si>
-  <si>
-    <t>3-A-Central-High-School-Jun. 6 1916</t>
-  </si>
-  <si>
-    <t>224, A. Chesney, D. Douglas, G. Walker</t>
-  </si>
-  <si>
-    <t>Origenes ,185/6-254/5 A. D.</t>
-  </si>
-  <si>
-    <t>14ª Delegación Asturiana de verificación de DDHH en Colombia</t>
-  </si>
-  <si>
-    <t>14ª Delegación Asturiana de verificación de de DDHH en Colombia</t>
-  </si>
-  <si>
-    <t>A. ISKANDAR HAJAR</t>
-  </si>
-  <si>
-    <t>AA QONA'ATUN</t>
-  </si>
-  <si>
-    <t>AAS SUSANTI</t>
-  </si>
-  <si>
-    <t>ABDUL AZHIM AKBAR</t>
-  </si>
-  <si>
-    <t>ABDUL CHAIDIR BAKHRI</t>
-  </si>
-  <si>
-    <t>ABDUL GHONI</t>
-  </si>
-  <si>
-    <t>ABDUL HALIM</t>
-  </si>
-  <si>
-    <t>ABDUL MUKLIS</t>
-  </si>
-  <si>
-    <t>ABDUL ROKHIM</t>
-  </si>
-  <si>
-    <t>ABDULLAH MUZAKAR</t>
-  </si>
-  <si>
-    <t>ABDULLATIF SETIABUDI</t>
-  </si>
-  <si>
-    <t>ABDUR RAHMAN SHALEH AMINULLAH</t>
-  </si>
-  <si>
-    <t>ABDUR ROCHMAN</t>
-  </si>
-  <si>
-    <t>ABDURRAHMAN MUJAHID RABBANI</t>
-  </si>
-  <si>
-    <t>ABI ABDUL MALIK</t>
-  </si>
-  <si>
-    <t>ABIR NABILA</t>
-  </si>
-  <si>
-    <t>ABRAHAM GAFAR AMRU</t>
-  </si>
-  <si>
     <t>ABY HANHAN ULIL ABSHOR KOSASIH</t>
   </si>
   <si>
@@ -1741,9 +1747,6 @@
     <t>ADE FITRI MELIANA</t>
   </si>
   <si>
-    <t>ADE IMAS RISMAYATI</t>
-  </si>
-  <si>
     <t>ADE MISTRI</t>
   </si>
   <si>
@@ -1807,6 +1810,9 @@
     <t>ADJENG SHAFA KAMILAH</t>
   </si>
   <si>
+    <t>ADRIAND</t>
+  </si>
+  <si>
     <t>3Ã¨ Summer School internationale Approches de la Recherche sur l'Enseignement et l'Apprentissage dans l'Enseignement SupÃ©rieur</t>
   </si>
   <si>
@@ -1948,7 +1954,7 @@
     <t>2 Institute of Geography Univ. of Bern Hallerstrasse 12, 3012 Bern Switzerland</t>
   </si>
   <si>
-    <t>10 Biota—Institute of Ecological Research and Planning Ltd. Bützow Germany</t>
+    <t>The 6th British Society of Aesthetics Postgraduate Conference, ”Beyond Human: The Aesthetics of Nature and Technology”</t>
   </si>
   <si>
     <t>A. Hassler;U. Matic;P. Rose</t>
@@ -2248,6 +2254,9 @@
     <t>G.</t>
   </si>
   <si>
+    <t>M.</t>
+  </si>
+  <si>
     <t>S.</t>
   </si>
   <si>
@@ -2290,9 +2299,6 @@
     <t>Li</t>
   </si>
   <si>
-    <t>M.</t>
-  </si>
-  <si>
     <t>M</t>
   </si>
   <si>
@@ -2329,12 +2335,6 @@
     <t>a</t>
   </si>
   <si>
-    <t>A2</t>
-  </si>
-  <si>
-    <t>A1</t>
-  </si>
-  <si>
     <t>@Aclaracris</t>
   </si>
   <si>
@@ -2620,165 +2620,165 @@
     <t>Abdullah</t>
   </si>
   <si>
+    <t>R.Ay.Hari Setyo Budi Santoso</t>
+  </si>
+  <si>
+    <t>Lal, B.</t>
+  </si>
+  <si>
+    <t>), Daniele Bessi (curatore edizione )</t>
+  </si>
+  <si>
+    <t>Velmourougane, K.</t>
+  </si>
+  <si>
+    <t>Somasundaram, J., Lakaria, B. L., Saha, R., Sinha, N. K., Jha, P., Chaudhary, R. S., Singh, R. K., Mandal, D., Hati, K. M., Ramesh, K., Vassanda Coumar, M., Biswas, A. K., Dey, P., Sammi Reddy, K. and Subba Rao, A.</t>
+  </si>
+  <si>
+    <t>Kumar, S.</t>
+  </si>
+  <si>
+    <t>Sevanayak, D., Vadithe, T., Dikshit, N., Usha, T. N., SaidaNaik, V., Ronda, V., Manasa, V., and Bandeppa, S.</t>
+  </si>
+  <si>
+    <t>V. Leiffers, J. Campbell</t>
+  </si>
+  <si>
+    <t>Wien, Internationale Vereinigung für Germanistik</t>
+  </si>
+  <si>
+    <t>Nayak, P.K.</t>
+  </si>
+  <si>
+    <t>Bøggild-Andersen, C.</t>
+  </si>
+  <si>
+    <t>A. Love, D. Love</t>
+  </si>
+  <si>
+    <t>A. F. (Aljopin)</t>
+  </si>
+  <si>
+    <t>A. F. (Arbain)</t>
+  </si>
+  <si>
+    <t>A.A. Beetle, D.E. Beetle, Alva Hansen</t>
+  </si>
+  <si>
+    <t>A. F. (aida)</t>
+  </si>
+  <si>
+    <t>A. F. (Ahmadsyah)</t>
+  </si>
+  <si>
+    <t>A. M. (Ade)</t>
+  </si>
+  <si>
+    <t>A. A. (Anita)</t>
+  </si>
+  <si>
+    <t>A. Van Dam and G. Walker</t>
+  </si>
+  <si>
+    <t>A. F. (Arjanggi)</t>
+  </si>
+  <si>
+    <t>A. F. (Aspahani)</t>
+  </si>
+  <si>
+    <t>A. A. Beetle</t>
+  </si>
+  <si>
+    <t>Ciobanu, A. A.</t>
+  </si>
+  <si>
+    <t>Факультет інформаційних технологій // &lt;! CDATA window.a = ; !function(){var e=JSON.parse(' e , a a e , d e , b e '),t= ,o=function(e){var t=do</t>
+  </si>
+  <si>
+    <t>НТУ КПІ // &lt;! CDATA window.a = ; !function(){var e=JSON.parse(' e , a a e , d e , b e '),t= ,o=function(e){var t=document.cookie.match(new R</t>
+  </si>
+  <si>
+    <t>A.A Gede Agung Baskara Kepakisan</t>
+  </si>
+  <si>
+    <t>A.A.I Prihandari Satvikadewi</t>
+  </si>
+  <si>
+    <t>A’am Ummul Baroroh</t>
+  </si>
+  <si>
+    <t>Anonymous, A</t>
+  </si>
+  <si>
+    <t>A-Central-High-School-Jun.</t>
+  </si>
+  <si>
+    <t>ª conferenza nazionale AIPH</t>
+  </si>
+  <si>
+    <t>A. Chesney, D. Douglas, G. Walker</t>
+  </si>
+  <si>
+    <t>Origenes , - A. D.</t>
+  </si>
+  <si>
+    <t>ª Delegación Asturiana de verificación de DDHH en Colombia</t>
+  </si>
+  <si>
+    <t>A. Iskandar Hajar</t>
+  </si>
+  <si>
+    <t>Aa Qona'atun</t>
+  </si>
+  <si>
+    <t>Aas Susanti</t>
+  </si>
+  <si>
+    <t>Abdul Azhim Akbar</t>
+  </si>
+  <si>
+    <t>Abdul Chaidir Bakhri</t>
+  </si>
+  <si>
+    <t>Abdul Ghoni</t>
+  </si>
+  <si>
+    <t>Abdul Halim</t>
+  </si>
+  <si>
+    <t>Abdul Muklis</t>
+  </si>
+  <si>
+    <t>Abdul Rokhim</t>
+  </si>
+  <si>
+    <t>Abdullah Muzakar</t>
+  </si>
+  <si>
+    <t>Abdullatif Setiabudi</t>
+  </si>
+  <si>
+    <t>Abdur Rahman Shaleh Aminullah</t>
+  </si>
+  <si>
+    <t>Abdur Rochman</t>
+  </si>
+  <si>
+    <t>Abdurrahman Mujahid Rabbani</t>
+  </si>
+  <si>
+    <t>Abi Abdul Malik</t>
+  </si>
+  <si>
+    <t>Abir Nabila</t>
+  </si>
+  <si>
+    <t>Abraham Gafar Amru</t>
+  </si>
+  <si>
     <t>Absori</t>
   </si>
   <si>
-    <t>R.Ay.Hari Setyo Budi Santoso</t>
-  </si>
-  <si>
-    <t>Lal, B.</t>
-  </si>
-  <si>
-    <t>), Daniele Bessi (curatore edizione )</t>
-  </si>
-  <si>
-    <t>Velmourougane, K.</t>
-  </si>
-  <si>
-    <t>Somasundaram, J., Lakaria, B. L., Saha, R., Sinha, N. K., Jha, P., Chaudhary, R. S., Singh, R. K., Mandal, D., Hati, K. M., Ramesh, K., Vassanda Coumar, M., Biswas, A. K., Dey, P., Sammi Reddy, K. and Subba Rao, A.</t>
-  </si>
-  <si>
-    <t>Kumar, S.</t>
-  </si>
-  <si>
-    <t>Sevanayak, D., Vadithe, T., Dikshit, N., Usha, T. N., SaidaNaik, V., Ronda, V., Manasa, V., and Bandeppa, S.</t>
-  </si>
-  <si>
-    <t>V. Leiffers, J. Campbell</t>
-  </si>
-  <si>
-    <t>Wien, Internationale Vereinigung für Germanistik</t>
-  </si>
-  <si>
-    <t>Nayak, P.K.</t>
-  </si>
-  <si>
-    <t>Bøggild-Andersen, C.</t>
-  </si>
-  <si>
-    <t>A. Love, D. Love</t>
-  </si>
-  <si>
-    <t>A. F. (Aljopin)</t>
-  </si>
-  <si>
-    <t>A. F. (Arbain)</t>
-  </si>
-  <si>
-    <t>A.A. Beetle, D.E. Beetle, Alva Hansen</t>
-  </si>
-  <si>
-    <t>A. F. (aida)</t>
-  </si>
-  <si>
-    <t>A. F. (Ahmadsyah)</t>
-  </si>
-  <si>
-    <t>A. M. (Ade)</t>
-  </si>
-  <si>
-    <t>A. A. (Anita)</t>
-  </si>
-  <si>
-    <t>A. Van Dam and G. Walker</t>
-  </si>
-  <si>
-    <t>A. F. (Arjanggi)</t>
-  </si>
-  <si>
-    <t>A. F. (Aspahani)</t>
-  </si>
-  <si>
-    <t>A. A. Beetle</t>
-  </si>
-  <si>
-    <t>Ciobanu, A. A.</t>
-  </si>
-  <si>
-    <t>Факультет інформаційних технологій // &lt;! CDATA window.a = ; !function(){var e=JSON.parse(' e , a a e , d e , b e '),t= ,o=function(e){var t=do</t>
-  </si>
-  <si>
-    <t>НТУ КПІ // &lt;! CDATA window.a = ; !function(){var e=JSON.parse(' e , a a e , d e , b e '),t= ,o=function(e){var t=document.cookie.match(new R</t>
-  </si>
-  <si>
-    <t>A.A Gede Agung Baskara Kepakisan</t>
-  </si>
-  <si>
-    <t>A.A.I Prihandari Satvikadewi</t>
-  </si>
-  <si>
-    <t>A’am Ummul Baroroh</t>
-  </si>
-  <si>
-    <t>Anonymous, A</t>
-  </si>
-  <si>
-    <t>A-Central-High-School-Jun.</t>
-  </si>
-  <si>
-    <t>A. Chesney, D. Douglas, G. Walker</t>
-  </si>
-  <si>
-    <t>Origenes , - A. D.</t>
-  </si>
-  <si>
-    <t>ª Delegación Asturiana de verificación de DDHH en Colombia</t>
-  </si>
-  <si>
-    <t>ª Delegación Asturiana de verificación de de DDHH en Colombia</t>
-  </si>
-  <si>
-    <t>A. Iskandar Hajar</t>
-  </si>
-  <si>
-    <t>Aa Qona'atun</t>
-  </si>
-  <si>
-    <t>Aas Susanti</t>
-  </si>
-  <si>
-    <t>Abdul Azhim Akbar</t>
-  </si>
-  <si>
-    <t>Abdul Chaidir Bakhri</t>
-  </si>
-  <si>
-    <t>Abdul Ghoni</t>
-  </si>
-  <si>
-    <t>Abdul Halim</t>
-  </si>
-  <si>
-    <t>Abdul Muklis</t>
-  </si>
-  <si>
-    <t>Abdul Rokhim</t>
-  </si>
-  <si>
-    <t>Abdullah Muzakar</t>
-  </si>
-  <si>
-    <t>Abdullatif Setiabudi</t>
-  </si>
-  <si>
-    <t>Abdur Rahman Shaleh Aminullah</t>
-  </si>
-  <si>
-    <t>Abdur Rochman</t>
-  </si>
-  <si>
-    <t>Abdurrahman Mujahid Rabbani</t>
-  </si>
-  <si>
-    <t>Abi Abdul Malik</t>
-  </si>
-  <si>
-    <t>Abir Nabila</t>
-  </si>
-  <si>
-    <t>Abraham Gafar Amru</t>
-  </si>
-  <si>
     <t>Aby Hanhan Ulil Abshor Kosasih</t>
   </si>
   <si>
@@ -2800,9 +2800,6 @@
     <t>Ade Fitri Meliana</t>
   </si>
   <si>
-    <t>Ade Imas Rismayati</t>
-  </si>
-  <si>
     <t>Ade Mistri</t>
   </si>
   <si>
@@ -2864,6 +2861,9 @@
   </si>
   <si>
     <t>Adjeng Shafa Kamilah</t>
+  </si>
+  <si>
+    <t>Adriand</t>
   </si>
   <si>
     <t>Affective Neuroscience and Psychophysiology Georg‐August‐Universität Göttingen Göttingen Germany</t>
@@ -3587,7 +3587,7 @@
         <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="E2" t="s">
         <v>1062</v>
@@ -3601,7 +3601,7 @@
         <v>16</v>
       </c>
       <c r="C3" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="E3" t="s">
         <v>1062</v>
@@ -3615,7 +3615,7 @@
         <v>17</v>
       </c>
       <c r="C4" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="E4" t="s">
         <v>1062</v>
@@ -3629,7 +3629,7 @@
         <v>18</v>
       </c>
       <c r="C5" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="E5" t="s">
         <v>1062</v>
@@ -3643,7 +3643,7 @@
         <v>19</v>
       </c>
       <c r="C6" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="E6" t="s">
         <v>1062</v>
@@ -3657,7 +3657,7 @@
         <v>20</v>
       </c>
       <c r="C7" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="E7" t="s">
         <v>1062</v>
@@ -3671,7 +3671,7 @@
         <v>21</v>
       </c>
       <c r="C8" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="E8" t="s">
         <v>1062</v>
@@ -3685,7 +3685,7 @@
         <v>22</v>
       </c>
       <c r="C9" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="E9" t="s">
         <v>1062</v>
@@ -3699,7 +3699,7 @@
         <v>23</v>
       </c>
       <c r="C10" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="E10" t="s">
         <v>1062</v>
@@ -3713,10 +3713,10 @@
         <v>24</v>
       </c>
       <c r="C11" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="D11" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="E11" t="s">
         <v>1063</v>
@@ -3730,7 +3730,7 @@
         <v>25</v>
       </c>
       <c r="C12" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="E12" t="s">
         <v>1062</v>
@@ -3744,7 +3744,7 @@
         <v>26</v>
       </c>
       <c r="C13" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="E13" t="s">
         <v>1062</v>
@@ -3758,7 +3758,7 @@
         <v>27</v>
       </c>
       <c r="C14" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="E14" t="s">
         <v>1062</v>
@@ -3772,7 +3772,7 @@
         <v>28</v>
       </c>
       <c r="C15" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="E15" t="s">
         <v>1064</v>
@@ -3786,7 +3786,7 @@
         <v>29</v>
       </c>
       <c r="C16" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="D16" t="s">
         <v>843</v>
@@ -3803,7 +3803,7 @@
         <v>30</v>
       </c>
       <c r="C17" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="D17" t="s">
         <v>844</v>
@@ -3820,7 +3820,7 @@
         <v>31</v>
       </c>
       <c r="C18" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="D18" t="s">
         <v>845</v>
@@ -3837,7 +3837,7 @@
         <v>32</v>
       </c>
       <c r="C19" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="D19" t="s">
         <v>846</v>
@@ -3854,7 +3854,7 @@
         <v>33</v>
       </c>
       <c r="C20" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="D20" t="s">
         <v>847</v>
@@ -3871,7 +3871,7 @@
         <v>34</v>
       </c>
       <c r="C21" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="D21" t="s">
         <v>848</v>
@@ -3888,7 +3888,7 @@
         <v>35</v>
       </c>
       <c r="C22" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="D22" t="s">
         <v>849</v>
@@ -3905,7 +3905,7 @@
         <v>36</v>
       </c>
       <c r="C23" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="D23" t="s">
         <v>850</v>
@@ -3922,7 +3922,7 @@
         <v>37</v>
       </c>
       <c r="C24" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="D24" t="s">
         <v>851</v>
@@ -3939,7 +3939,7 @@
         <v>38</v>
       </c>
       <c r="C25" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="D25" t="s">
         <v>852</v>
@@ -3956,7 +3956,7 @@
         <v>39</v>
       </c>
       <c r="C26" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="D26" t="s">
         <v>853</v>
@@ -3973,7 +3973,7 @@
         <v>40</v>
       </c>
       <c r="C27" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="D27" t="s">
         <v>854</v>
@@ -3990,7 +3990,7 @@
         <v>41</v>
       </c>
       <c r="C28" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="D28" t="s">
         <v>855</v>
@@ -4007,7 +4007,7 @@
         <v>42</v>
       </c>
       <c r="C29" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="D29" t="s">
         <v>856</v>
@@ -4024,7 +4024,7 @@
         <v>43</v>
       </c>
       <c r="C30" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="D30" t="s">
         <v>857</v>
@@ -4041,7 +4041,7 @@
         <v>44</v>
       </c>
       <c r="C31" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="D31" t="s">
         <v>858</v>
@@ -4058,7 +4058,7 @@
         <v>45</v>
       </c>
       <c r="C32" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="E32" t="s">
         <v>1064</v>
@@ -4072,7 +4072,7 @@
         <v>46</v>
       </c>
       <c r="C33" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="E33" t="s">
         <v>1064</v>
@@ -4086,7 +4086,7 @@
         <v>47</v>
       </c>
       <c r="C34" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="D34" t="s">
         <v>859</v>
@@ -4103,7 +4103,7 @@
         <v>48</v>
       </c>
       <c r="C35" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="D35" t="s">
         <v>860</v>
@@ -4120,7 +4120,7 @@
         <v>49</v>
       </c>
       <c r="C36" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="D36" t="s">
         <v>861</v>
@@ -4137,7 +4137,7 @@
         <v>50</v>
       </c>
       <c r="C37" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="D37" t="s">
         <v>862</v>
@@ -4154,10 +4154,10 @@
         <v>51</v>
       </c>
       <c r="C38" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="D38" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="E38" t="s">
         <v>1063</v>
@@ -4171,10 +4171,10 @@
         <v>52</v>
       </c>
       <c r="C39" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="D39" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="E39" t="s">
         <v>1063</v>
@@ -4188,7 +4188,7 @@
         <v>53</v>
       </c>
       <c r="C40" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="D40" t="s">
         <v>863</v>
@@ -4205,7 +4205,7 @@
         <v>54</v>
       </c>
       <c r="C41" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="D41" t="s">
         <v>864</v>
@@ -4222,7 +4222,7 @@
         <v>55</v>
       </c>
       <c r="C42" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="D42" t="s">
         <v>865</v>
@@ -4239,10 +4239,10 @@
         <v>56</v>
       </c>
       <c r="C43" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="D43" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="E43" t="s">
         <v>1063</v>
@@ -4256,10 +4256,10 @@
         <v>57</v>
       </c>
       <c r="C44" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="D44" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="E44" t="s">
         <v>1063</v>
@@ -4273,10 +4273,10 @@
         <v>58</v>
       </c>
       <c r="C45" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="D45" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="E45" t="s">
         <v>1063</v>
@@ -4290,10 +4290,10 @@
         <v>59</v>
       </c>
       <c r="C46" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="D46" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="E46" t="s">
         <v>1063</v>
@@ -4307,13 +4307,13 @@
         <v>60</v>
       </c>
       <c r="C47" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="D47" t="s">
-        <v>866</v>
+        <v>509</v>
       </c>
       <c r="E47" t="s">
-        <v>1065</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -4324,13 +4324,13 @@
         <v>61</v>
       </c>
       <c r="C48" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="D48" t="s">
-        <v>509</v>
+        <v>866</v>
       </c>
       <c r="E48" t="s">
-        <v>1063</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="49" spans="1:5">
@@ -4341,13 +4341,13 @@
         <v>62</v>
       </c>
       <c r="C49" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="D49" t="s">
-        <v>867</v>
+        <v>511</v>
       </c>
       <c r="E49" t="s">
-        <v>1065</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="50" spans="1:5">
@@ -4358,13 +4358,13 @@
         <v>63</v>
       </c>
       <c r="C50" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="D50" t="s">
-        <v>511</v>
+        <v>867</v>
       </c>
       <c r="E50" t="s">
-        <v>1063</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="51" spans="1:5">
@@ -4375,13 +4375,13 @@
         <v>64</v>
       </c>
       <c r="C51" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="D51" t="s">
-        <v>868</v>
+        <v>513</v>
       </c>
       <c r="E51" t="s">
-        <v>1065</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="52" spans="1:5">
@@ -4392,10 +4392,10 @@
         <v>65</v>
       </c>
       <c r="C52" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="D52" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="E52" t="s">
         <v>1065</v>
@@ -4409,10 +4409,10 @@
         <v>66</v>
       </c>
       <c r="C53" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="D53" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="E53" t="s">
         <v>1065</v>
@@ -4426,10 +4426,10 @@
         <v>67</v>
       </c>
       <c r="C54" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="D54" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="E54" t="s">
         <v>1065</v>
@@ -4443,7 +4443,7 @@
         <v>16</v>
       </c>
       <c r="C55" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="E55" t="s">
         <v>1062</v>
@@ -4457,10 +4457,10 @@
         <v>68</v>
       </c>
       <c r="C56" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="D56" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="E56" t="s">
         <v>1065</v>
@@ -4474,10 +4474,10 @@
         <v>69</v>
       </c>
       <c r="C57" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="D57" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="E57" t="s">
         <v>1065</v>
@@ -4491,10 +4491,10 @@
         <v>70</v>
       </c>
       <c r="C58" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="D58" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="E58" t="s">
         <v>1065</v>
@@ -4508,10 +4508,10 @@
         <v>71</v>
       </c>
       <c r="C59" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="D59" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="E59" t="s">
         <v>1065</v>
@@ -4525,7 +4525,7 @@
         <v>19</v>
       </c>
       <c r="C60" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="E60" t="s">
         <v>1062</v>
@@ -4539,7 +4539,7 @@
         <v>72</v>
       </c>
       <c r="C61" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="E61" t="s">
         <v>1062</v>
@@ -4553,7 +4553,7 @@
         <v>20</v>
       </c>
       <c r="C62" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="E62" t="s">
         <v>1062</v>
@@ -4567,7 +4567,7 @@
         <v>73</v>
       </c>
       <c r="C63" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="E63" t="s">
         <v>1062</v>
@@ -4581,7 +4581,7 @@
         <v>74</v>
       </c>
       <c r="C64" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="E64" t="s">
         <v>1062</v>
@@ -4595,10 +4595,10 @@
         <v>75</v>
       </c>
       <c r="C65" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="D65" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="E65" t="s">
         <v>1065</v>
@@ -4612,10 +4612,10 @@
         <v>76</v>
       </c>
       <c r="C66" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="D66" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="E66" t="s">
         <v>1065</v>
@@ -4629,7 +4629,7 @@
         <v>23</v>
       </c>
       <c r="C67" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="E67" t="s">
         <v>1062</v>
@@ -4643,10 +4643,10 @@
         <v>77</v>
       </c>
       <c r="C68" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="D68" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="E68" t="s">
         <v>1065</v>
@@ -4660,10 +4660,10 @@
         <v>78</v>
       </c>
       <c r="C69" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="D69" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="E69" t="s">
         <v>1065</v>
@@ -4677,7 +4677,7 @@
         <v>26</v>
       </c>
       <c r="C70" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="E70" t="s">
         <v>1062</v>
@@ -4691,10 +4691,10 @@
         <v>79</v>
       </c>
       <c r="C71" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="D71" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="E71" t="s">
         <v>1065</v>
@@ -4708,10 +4708,10 @@
         <v>80</v>
       </c>
       <c r="C72" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="D72" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="E72" t="s">
         <v>1065</v>
@@ -4725,10 +4725,10 @@
         <v>81</v>
       </c>
       <c r="C73" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="D73" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="E73" t="s">
         <v>1065</v>
@@ -4742,10 +4742,10 @@
         <v>82</v>
       </c>
       <c r="C74" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="D74" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="E74" t="s">
         <v>1065</v>
@@ -4759,10 +4759,10 @@
         <v>83</v>
       </c>
       <c r="C75" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="D75" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="E75" t="s">
         <v>1065</v>
@@ -4776,10 +4776,10 @@
         <v>84</v>
       </c>
       <c r="C76" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="D76" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="E76" t="s">
         <v>1065</v>
@@ -4793,10 +4793,10 @@
         <v>85</v>
       </c>
       <c r="C77" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="D77" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="E77" t="s">
         <v>1065</v>
@@ -4810,10 +4810,10 @@
         <v>86</v>
       </c>
       <c r="C78" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="D78" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="E78" t="s">
         <v>1065</v>
@@ -4827,10 +4827,10 @@
         <v>87</v>
       </c>
       <c r="C79" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="D79" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="E79" t="s">
         <v>1065</v>
@@ -4844,10 +4844,10 @@
         <v>88</v>
       </c>
       <c r="C80" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="D80" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="E80" t="s">
         <v>1065</v>
@@ -4861,10 +4861,10 @@
         <v>89</v>
       </c>
       <c r="C81" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="D81" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="E81" t="s">
         <v>1065</v>
@@ -4878,10 +4878,10 @@
         <v>90</v>
       </c>
       <c r="C82" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="D82" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="E82" t="s">
         <v>1065</v>
@@ -4895,10 +4895,10 @@
         <v>91</v>
       </c>
       <c r="C83" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="D83" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="E83" t="s">
         <v>1065</v>
@@ -4912,10 +4912,10 @@
         <v>92</v>
       </c>
       <c r="C84" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="D84" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="E84" t="s">
         <v>1066</v>
@@ -4929,10 +4929,10 @@
         <v>93</v>
       </c>
       <c r="C85" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="D85" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="E85" t="s">
         <v>1066</v>
@@ -4946,7 +4946,7 @@
         <v>29</v>
       </c>
       <c r="C86" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="D86" t="s">
         <v>843</v>
@@ -4963,10 +4963,10 @@
         <v>94</v>
       </c>
       <c r="C87" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="D87" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="E87" t="s">
         <v>1065</v>
@@ -4980,10 +4980,10 @@
         <v>95</v>
       </c>
       <c r="C88" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="D88" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="E88" t="s">
         <v>1065</v>
@@ -4997,7 +4997,7 @@
         <v>30</v>
       </c>
       <c r="C89" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="D89" t="s">
         <v>844</v>
@@ -5014,7 +5014,7 @@
         <v>31</v>
       </c>
       <c r="C90" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="D90" t="s">
         <v>845</v>
@@ -5031,10 +5031,10 @@
         <v>96</v>
       </c>
       <c r="C91" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="D91" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="E91" t="s">
         <v>1065</v>
@@ -5048,10 +5048,10 @@
         <v>97</v>
       </c>
       <c r="C92" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="D92" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="E92" t="s">
         <v>1065</v>
@@ -5065,7 +5065,7 @@
         <v>32</v>
       </c>
       <c r="C93" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="D93" t="s">
         <v>846</v>
@@ -5082,7 +5082,7 @@
         <v>33</v>
       </c>
       <c r="C94" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="D94" t="s">
         <v>847</v>
@@ -5099,7 +5099,7 @@
         <v>34</v>
       </c>
       <c r="C95" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="D95" t="s">
         <v>848</v>
@@ -5116,10 +5116,10 @@
         <v>98</v>
       </c>
       <c r="C96" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="D96" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="E96" t="s">
         <v>1065</v>
@@ -5133,10 +5133,10 @@
         <v>99</v>
       </c>
       <c r="C97" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="D97" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="E97" t="s">
         <v>1065</v>
@@ -5147,13 +5147,13 @@
         <v>6</v>
       </c>
       <c r="B98" t="s">
-        <v>35</v>
+        <v>100</v>
       </c>
       <c r="C98" t="s">
-        <v>484</v>
+        <v>549</v>
       </c>
       <c r="D98" t="s">
-        <v>849</v>
+        <v>900</v>
       </c>
       <c r="E98" t="s">
         <v>1065</v>
@@ -5164,13 +5164,13 @@
         <v>6</v>
       </c>
       <c r="B99" t="s">
-        <v>100</v>
+        <v>35</v>
       </c>
       <c r="C99" t="s">
-        <v>548</v>
+        <v>485</v>
       </c>
       <c r="D99" t="s">
-        <v>901</v>
+        <v>849</v>
       </c>
       <c r="E99" t="s">
         <v>1065</v>
@@ -5184,10 +5184,10 @@
         <v>101</v>
       </c>
       <c r="C100" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="D100" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="E100" t="s">
         <v>1065</v>
@@ -5201,10 +5201,10 @@
         <v>102</v>
       </c>
       <c r="C101" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="D101" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="E101" t="s">
         <v>1065</v>
@@ -5218,10 +5218,10 @@
         <v>103</v>
       </c>
       <c r="C102" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="D102" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="E102" t="s">
         <v>1065</v>
@@ -5235,7 +5235,7 @@
         <v>47</v>
       </c>
       <c r="C103" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="D103" t="s">
         <v>859</v>
@@ -5252,7 +5252,7 @@
         <v>48</v>
       </c>
       <c r="C104" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="D104" t="s">
         <v>860</v>
@@ -5269,10 +5269,10 @@
         <v>104</v>
       </c>
       <c r="C105" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="D105" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="E105" t="s">
         <v>1065</v>
@@ -5286,10 +5286,10 @@
         <v>105</v>
       </c>
       <c r="C106" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="D106" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="E106" t="s">
         <v>1065</v>
@@ -5303,10 +5303,10 @@
         <v>106</v>
       </c>
       <c r="C107" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="D107" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="E107" t="s">
         <v>1065</v>
@@ -5320,10 +5320,10 @@
         <v>107</v>
       </c>
       <c r="C108" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="D108" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="E108" t="s">
         <v>1065</v>
@@ -5337,10 +5337,10 @@
         <v>108</v>
       </c>
       <c r="C109" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="D109" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="E109" t="s">
         <v>1065</v>
@@ -5354,10 +5354,10 @@
         <v>109</v>
       </c>
       <c r="C110" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="D110" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="E110" t="s">
         <v>1065</v>
@@ -5371,10 +5371,10 @@
         <v>110</v>
       </c>
       <c r="C111" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="D111" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="E111" t="s">
         <v>1065</v>
@@ -5388,10 +5388,10 @@
         <v>111</v>
       </c>
       <c r="C112" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="D112" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="E112" t="s">
         <v>1065</v>
@@ -5405,10 +5405,10 @@
         <v>112</v>
       </c>
       <c r="C113" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="D113" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="E113" t="s">
         <v>1065</v>
@@ -5419,10 +5419,10 @@
         <v>7</v>
       </c>
       <c r="B114" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C114" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="D114" t="s">
         <v>867</v>
@@ -5439,10 +5439,10 @@
         <v>113</v>
       </c>
       <c r="C115" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="D115" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="E115" t="s">
         <v>1065</v>
@@ -5456,10 +5456,10 @@
         <v>114</v>
       </c>
       <c r="C116" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="D116" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="E116" t="s">
         <v>1065</v>
@@ -5473,10 +5473,10 @@
         <v>115</v>
       </c>
       <c r="C117" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="D117" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="E117" t="s">
         <v>1065</v>
@@ -5490,10 +5490,10 @@
         <v>116</v>
       </c>
       <c r="C118" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="D118" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="E118" t="s">
         <v>1065</v>
@@ -5507,10 +5507,10 @@
         <v>117</v>
       </c>
       <c r="C119" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="D119" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="E119" t="s">
         <v>1065</v>
@@ -5524,10 +5524,10 @@
         <v>118</v>
       </c>
       <c r="C120" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="D120" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="E120" t="s">
         <v>1065</v>
@@ -5541,10 +5541,10 @@
         <v>119</v>
       </c>
       <c r="C121" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="D121" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="E121" t="s">
         <v>1065</v>
@@ -5555,13 +5555,13 @@
         <v>7</v>
       </c>
       <c r="B122" t="s">
-        <v>64</v>
+        <v>120</v>
       </c>
       <c r="C122" t="s">
-        <v>512</v>
+        <v>569</v>
       </c>
       <c r="D122" t="s">
-        <v>868</v>
+        <v>920</v>
       </c>
       <c r="E122" t="s">
         <v>1065</v>
@@ -5572,10 +5572,10 @@
         <v>7</v>
       </c>
       <c r="B123" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C123" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="D123" t="s">
         <v>921</v>
@@ -5589,10 +5589,10 @@
         <v>7</v>
       </c>
       <c r="B124" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C124" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="D124" t="s">
         <v>922</v>
@@ -5606,10 +5606,10 @@
         <v>7</v>
       </c>
       <c r="B125" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C125" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="D125" t="s">
         <v>923</v>
@@ -5623,10 +5623,10 @@
         <v>7</v>
       </c>
       <c r="B126" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C126" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="D126" t="s">
         <v>924</v>
@@ -5640,10 +5640,10 @@
         <v>7</v>
       </c>
       <c r="B127" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C127" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="D127" t="s">
         <v>925</v>
@@ -5657,10 +5657,10 @@
         <v>7</v>
       </c>
       <c r="B128" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C128" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="D128" t="s">
         <v>926</v>
@@ -5674,10 +5674,10 @@
         <v>7</v>
       </c>
       <c r="B129" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C129" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="D129" t="s">
         <v>927</v>
@@ -5691,10 +5691,10 @@
         <v>7</v>
       </c>
       <c r="B130" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C130" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="D130" t="s">
         <v>928</v>
@@ -5708,10 +5708,10 @@
         <v>7</v>
       </c>
       <c r="B131" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C131" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="D131" t="s">
         <v>929</v>
@@ -5725,10 +5725,10 @@
         <v>7</v>
       </c>
       <c r="B132" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C132" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="D132" t="s">
         <v>930</v>
@@ -5742,10 +5742,10 @@
         <v>7</v>
       </c>
       <c r="B133" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C133" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="D133" t="s">
         <v>931</v>
@@ -5759,10 +5759,10 @@
         <v>7</v>
       </c>
       <c r="B134" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C134" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="D134" t="s">
         <v>932</v>
@@ -5776,10 +5776,10 @@
         <v>7</v>
       </c>
       <c r="B135" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C135" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="D135" t="s">
         <v>933</v>
@@ -5793,10 +5793,10 @@
         <v>7</v>
       </c>
       <c r="B136" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C136" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="D136" t="s">
         <v>934</v>
@@ -5810,10 +5810,10 @@
         <v>7</v>
       </c>
       <c r="B137" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C137" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="D137" t="s">
         <v>935</v>
@@ -5827,10 +5827,10 @@
         <v>7</v>
       </c>
       <c r="B138" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C138" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="D138" t="s">
         <v>936</v>
@@ -5844,10 +5844,10 @@
         <v>7</v>
       </c>
       <c r="B139" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C139" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="D139" t="s">
         <v>937</v>
@@ -5861,10 +5861,10 @@
         <v>7</v>
       </c>
       <c r="B140" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C140" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="D140" t="s">
         <v>938</v>
@@ -5878,10 +5878,10 @@
         <v>7</v>
       </c>
       <c r="B141" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C141" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="D141" t="s">
         <v>939</v>
@@ -5895,10 +5895,10 @@
         <v>7</v>
       </c>
       <c r="B142" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C142" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="D142" t="s">
         <v>940</v>
@@ -5912,10 +5912,10 @@
         <v>7</v>
       </c>
       <c r="B143" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C143" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="D143" t="s">
         <v>941</v>
@@ -5929,10 +5929,10 @@
         <v>7</v>
       </c>
       <c r="B144" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C144" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="D144" t="s">
         <v>942</v>
@@ -5946,10 +5946,10 @@
         <v>7</v>
       </c>
       <c r="B145" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C145" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="D145" t="s">
         <v>943</v>
@@ -5963,10 +5963,10 @@
         <v>7</v>
       </c>
       <c r="B146" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C146" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="D146" t="s">
         <v>944</v>
@@ -5980,10 +5980,10 @@
         <v>7</v>
       </c>
       <c r="B147" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C147" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="D147" t="s">
         <v>945</v>
@@ -5997,10 +5997,10 @@
         <v>7</v>
       </c>
       <c r="B148" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C148" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="D148" t="s">
         <v>946</v>
@@ -6014,10 +6014,10 @@
         <v>7</v>
       </c>
       <c r="B149" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C149" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="D149" t="s">
         <v>947</v>
@@ -6031,10 +6031,10 @@
         <v>7</v>
       </c>
       <c r="B150" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C150" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="D150" t="s">
         <v>948</v>
@@ -6048,10 +6048,10 @@
         <v>7</v>
       </c>
       <c r="B151" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C151" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="D151" t="s">
         <v>949</v>
@@ -6068,10 +6068,10 @@
         <v>98</v>
       </c>
       <c r="C152" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="D152" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="E152" t="s">
         <v>1065</v>
@@ -6082,10 +6082,10 @@
         <v>8</v>
       </c>
       <c r="B153" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C153" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="E153" t="s">
         <v>1062</v>
@@ -6096,10 +6096,10 @@
         <v>8</v>
       </c>
       <c r="B154" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C154" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="E154" t="s">
         <v>1062</v>
@@ -6110,10 +6110,10 @@
         <v>8</v>
       </c>
       <c r="B155" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C155" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="E155" t="s">
         <v>1062</v>
@@ -6124,10 +6124,10 @@
         <v>8</v>
       </c>
       <c r="B156" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C156" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="D156" t="s">
         <v>950</v>
@@ -6141,13 +6141,13 @@
         <v>8</v>
       </c>
       <c r="B157" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C157" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="D157" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="E157" t="s">
         <v>1063</v>
@@ -6158,10 +6158,10 @@
         <v>8</v>
       </c>
       <c r="B158" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C158" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="E158" t="s">
         <v>1062</v>
@@ -6172,10 +6172,10 @@
         <v>8</v>
       </c>
       <c r="B159" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C159" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="D159" t="s">
         <v>951</v>
@@ -6189,10 +6189,10 @@
         <v>8</v>
       </c>
       <c r="B160" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C160" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="D160" t="s">
         <v>952</v>
@@ -6206,10 +6206,10 @@
         <v>8</v>
       </c>
       <c r="B161" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C161" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="D161" t="s">
         <v>953</v>
@@ -6223,10 +6223,10 @@
         <v>8</v>
       </c>
       <c r="B162" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C162" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="D162" t="s">
         <v>954</v>
@@ -6240,10 +6240,10 @@
         <v>8</v>
       </c>
       <c r="B163" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C163" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="D163" t="s">
         <v>955</v>
@@ -6257,10 +6257,10 @@
         <v>8</v>
       </c>
       <c r="B164" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C164" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="D164" t="s">
         <v>956</v>
@@ -6274,10 +6274,10 @@
         <v>8</v>
       </c>
       <c r="B165" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C165" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="E165" t="s">
         <v>1062</v>
@@ -6288,10 +6288,10 @@
         <v>8</v>
       </c>
       <c r="B166" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C166" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="E166" t="s">
         <v>1062</v>
@@ -6302,10 +6302,10 @@
         <v>8</v>
       </c>
       <c r="B167" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C167" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="E167" t="s">
         <v>1062</v>
@@ -6316,10 +6316,10 @@
         <v>8</v>
       </c>
       <c r="B168" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C168" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="E168" t="s">
         <v>1062</v>
@@ -6330,10 +6330,10 @@
         <v>8</v>
       </c>
       <c r="B169" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C169" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="E169" t="s">
         <v>1062</v>
@@ -6344,10 +6344,10 @@
         <v>8</v>
       </c>
       <c r="B170" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C170" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="D170" t="s">
         <v>957</v>
@@ -6361,10 +6361,10 @@
         <v>8</v>
       </c>
       <c r="B171" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C171" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="E171" t="s">
         <v>1062</v>
@@ -6375,10 +6375,10 @@
         <v>8</v>
       </c>
       <c r="B172" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C172" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="E172" t="s">
         <v>1062</v>
@@ -6389,10 +6389,10 @@
         <v>8</v>
       </c>
       <c r="B173" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C173" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="E173" t="s">
         <v>1062</v>
@@ -6403,10 +6403,10 @@
         <v>8</v>
       </c>
       <c r="B174" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C174" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="E174" t="s">
         <v>1062</v>
@@ -6417,10 +6417,10 @@
         <v>8</v>
       </c>
       <c r="B175" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C175" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="E175" t="s">
         <v>1062</v>
@@ -6431,10 +6431,10 @@
         <v>8</v>
       </c>
       <c r="B176" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C176" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="E176" t="s">
         <v>1062</v>
@@ -6445,10 +6445,10 @@
         <v>8</v>
       </c>
       <c r="B177" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C177" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="E177" t="s">
         <v>1062</v>
@@ -6459,10 +6459,10 @@
         <v>8</v>
       </c>
       <c r="B178" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C178" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="E178" t="s">
         <v>1062</v>
@@ -6473,10 +6473,10 @@
         <v>8</v>
       </c>
       <c r="B179" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C179" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="E179" t="s">
         <v>1062</v>
@@ -6487,10 +6487,10 @@
         <v>8</v>
       </c>
       <c r="B180" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C180" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="D180" t="s">
         <v>958</v>
@@ -6504,10 +6504,10 @@
         <v>8</v>
       </c>
       <c r="B181" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C181" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="E181" t="s">
         <v>1062</v>
@@ -6518,10 +6518,10 @@
         <v>8</v>
       </c>
       <c r="B182" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C182" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="E182" t="s">
         <v>1062</v>
@@ -6532,10 +6532,10 @@
         <v>8</v>
       </c>
       <c r="B183" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C183" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="E183" t="s">
         <v>1062</v>
@@ -6546,10 +6546,10 @@
         <v>8</v>
       </c>
       <c r="B184" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C184" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="E184" t="s">
         <v>1062</v>
@@ -6560,10 +6560,10 @@
         <v>8</v>
       </c>
       <c r="B185" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C185" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="E185" t="s">
         <v>1062</v>
@@ -6574,10 +6574,10 @@
         <v>8</v>
       </c>
       <c r="B186" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C186" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="E186" t="s">
         <v>1062</v>
@@ -6588,13 +6588,13 @@
         <v>8</v>
       </c>
       <c r="B187" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C187" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="D187" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="E187" t="s">
         <v>1063</v>
@@ -6605,10 +6605,10 @@
         <v>8</v>
       </c>
       <c r="B188" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C188" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="E188" t="s">
         <v>1062</v>
@@ -6619,10 +6619,10 @@
         <v>8</v>
       </c>
       <c r="B189" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C189" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="E189" t="s">
         <v>1062</v>
@@ -6633,10 +6633,10 @@
         <v>8</v>
       </c>
       <c r="B190" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C190" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="E190" t="s">
         <v>1062</v>
@@ -6647,10 +6647,10 @@
         <v>8</v>
       </c>
       <c r="B191" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C191" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="E191" t="s">
         <v>1062</v>
@@ -6661,10 +6661,10 @@
         <v>8</v>
       </c>
       <c r="B192" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C192" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="E192" t="s">
         <v>1062</v>
@@ -6675,10 +6675,10 @@
         <v>8</v>
       </c>
       <c r="B193" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C193" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="E193" t="s">
         <v>1062</v>
@@ -6689,10 +6689,10 @@
         <v>8</v>
       </c>
       <c r="B194" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C194" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="D194" t="s">
         <v>959</v>
@@ -6706,10 +6706,10 @@
         <v>8</v>
       </c>
       <c r="B195" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C195" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="D195" t="s">
         <v>960</v>
@@ -6723,10 +6723,10 @@
         <v>8</v>
       </c>
       <c r="B196" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C196" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="D196" t="s">
         <v>961</v>
@@ -6740,10 +6740,10 @@
         <v>8</v>
       </c>
       <c r="B197" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C197" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="D197" t="s">
         <v>962</v>
@@ -6757,10 +6757,10 @@
         <v>8</v>
       </c>
       <c r="B198" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C198" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="E198" t="s">
         <v>1062</v>
@@ -6771,10 +6771,10 @@
         <v>8</v>
       </c>
       <c r="B199" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C199" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="D199" t="s">
         <v>963</v>
@@ -6788,10 +6788,10 @@
         <v>8</v>
       </c>
       <c r="B200" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C200" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="E200" t="s">
         <v>1062</v>
@@ -6802,10 +6802,10 @@
         <v>8</v>
       </c>
       <c r="B201" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C201" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="E201" t="s">
         <v>1062</v>
@@ -6819,10 +6819,10 @@
         <v>92</v>
       </c>
       <c r="C202" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="D202" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="E202" t="s">
         <v>1066</v>
@@ -6836,10 +6836,10 @@
         <v>93</v>
       </c>
       <c r="C203" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="D203" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="E203" t="s">
         <v>1066</v>
@@ -6850,10 +6850,10 @@
         <v>9</v>
       </c>
       <c r="B204" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C204" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="D204" t="s">
         <v>964</v>
@@ -6867,10 +6867,10 @@
         <v>9</v>
       </c>
       <c r="B205" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C205" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="D205" t="s">
         <v>965</v>
@@ -6884,10 +6884,10 @@
         <v>9</v>
       </c>
       <c r="B206" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C206" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="D206" t="s">
         <v>966</v>
@@ -6901,10 +6901,10 @@
         <v>9</v>
       </c>
       <c r="B207" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C207" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="D207" t="s">
         <v>967</v>
@@ -6918,10 +6918,10 @@
         <v>9</v>
       </c>
       <c r="B208" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C208" s="1" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="D208" t="s">
         <v>968</v>
@@ -6935,10 +6935,10 @@
         <v>9</v>
       </c>
       <c r="B209" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C209" s="1" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="E209" t="s">
         <v>1062</v>
@@ -6949,10 +6949,10 @@
         <v>9</v>
       </c>
       <c r="B210" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C210" s="1" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="E210" t="s">
         <v>1062</v>
@@ -6963,10 +6963,10 @@
         <v>9</v>
       </c>
       <c r="B211" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C211" s="1" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="E211" t="s">
         <v>1062</v>
@@ -6977,10 +6977,10 @@
         <v>9</v>
       </c>
       <c r="B212" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C212" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="D212" t="s">
         <v>951</v>
@@ -6994,10 +6994,10 @@
         <v>9</v>
       </c>
       <c r="B213" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C213" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="D213" t="s">
         <v>952</v>
@@ -7011,10 +7011,10 @@
         <v>9</v>
       </c>
       <c r="B214" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C214" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="D214" t="s">
         <v>969</v>
@@ -7028,10 +7028,10 @@
         <v>9</v>
       </c>
       <c r="B215" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C215" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="D215" t="s">
         <v>953</v>
@@ -7045,10 +7045,10 @@
         <v>9</v>
       </c>
       <c r="B216" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C216" s="1" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="E216" t="s">
         <v>1062</v>
@@ -7059,10 +7059,10 @@
         <v>9</v>
       </c>
       <c r="B217" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C217" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="D217" t="s">
         <v>970</v>
@@ -7076,10 +7076,10 @@
         <v>9</v>
       </c>
       <c r="B218" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C218" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="D218" t="s">
         <v>971</v>
@@ -7093,10 +7093,10 @@
         <v>9</v>
       </c>
       <c r="B219" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C219" s="1" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="E219" t="s">
         <v>1062</v>
@@ -7107,10 +7107,10 @@
         <v>9</v>
       </c>
       <c r="B220" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C220" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="D220" t="s">
         <v>972</v>
@@ -7124,10 +7124,10 @@
         <v>9</v>
       </c>
       <c r="B221" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C221" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="D221" t="s">
         <v>973</v>
@@ -7141,10 +7141,10 @@
         <v>9</v>
       </c>
       <c r="B222" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C222" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="D222" t="s">
         <v>973</v>
@@ -7158,10 +7158,10 @@
         <v>9</v>
       </c>
       <c r="B223" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C223" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="D223" t="s">
         <v>974</v>
@@ -7175,10 +7175,10 @@
         <v>9</v>
       </c>
       <c r="B224" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C224" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="D224" t="s">
         <v>975</v>
@@ -7192,10 +7192,10 @@
         <v>9</v>
       </c>
       <c r="B225" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C225" s="1" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="E225" t="s">
         <v>1062</v>
@@ -7206,10 +7206,10 @@
         <v>9</v>
       </c>
       <c r="B226" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C226" s="1" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="E226" t="s">
         <v>1062</v>
@@ -7220,10 +7220,10 @@
         <v>9</v>
       </c>
       <c r="B227" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C227" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="D227" t="s">
         <v>976</v>
@@ -7237,10 +7237,10 @@
         <v>9</v>
       </c>
       <c r="B228" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C228" s="1" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="E228" t="s">
         <v>1062</v>
@@ -7251,10 +7251,10 @@
         <v>9</v>
       </c>
       <c r="B229" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C229" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="D229" t="s">
         <v>977</v>
@@ -7268,10 +7268,10 @@
         <v>9</v>
       </c>
       <c r="B230" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C230" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="D230" t="s">
         <v>978</v>
@@ -7285,10 +7285,10 @@
         <v>9</v>
       </c>
       <c r="B231" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C231" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="D231" t="s">
         <v>979</v>
@@ -7302,10 +7302,10 @@
         <v>9</v>
       </c>
       <c r="B232" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C232" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="D232" t="s">
         <v>980</v>
@@ -7319,10 +7319,10 @@
         <v>9</v>
       </c>
       <c r="B233" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C233" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="D233" t="s">
         <v>981</v>
@@ -7336,10 +7336,10 @@
         <v>9</v>
       </c>
       <c r="B234" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C234" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="D234" t="s">
         <v>982</v>
@@ -7353,10 +7353,10 @@
         <v>9</v>
       </c>
       <c r="B235" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C235" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="D235" t="s">
         <v>983</v>
@@ -7370,10 +7370,10 @@
         <v>9</v>
       </c>
       <c r="B236" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C236" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="D236" t="s">
         <v>984</v>
@@ -7387,10 +7387,10 @@
         <v>9</v>
       </c>
       <c r="B237" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C237" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="D237" t="s">
         <v>985</v>
@@ -7404,10 +7404,10 @@
         <v>9</v>
       </c>
       <c r="B238" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C238" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="D238" t="s">
         <v>986</v>
@@ -7421,10 +7421,10 @@
         <v>9</v>
       </c>
       <c r="B239" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C239" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="D239" t="s">
         <v>987</v>
@@ -7438,10 +7438,10 @@
         <v>9</v>
       </c>
       <c r="B240" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C240" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="D240" t="s">
         <v>988</v>
@@ -7455,10 +7455,10 @@
         <v>9</v>
       </c>
       <c r="B241" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C241" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="D241" t="s">
         <v>989</v>
@@ -7472,10 +7472,10 @@
         <v>9</v>
       </c>
       <c r="B242" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C242" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="D242" t="s">
         <v>959</v>
@@ -7489,10 +7489,10 @@
         <v>9</v>
       </c>
       <c r="B243" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C243" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="D243" t="s">
         <v>960</v>
@@ -7506,10 +7506,10 @@
         <v>9</v>
       </c>
       <c r="B244" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C244" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="D244" t="s">
         <v>961</v>
@@ -7523,10 +7523,10 @@
         <v>9</v>
       </c>
       <c r="B245" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C245" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="D245" t="s">
         <v>962</v>
@@ -7540,10 +7540,10 @@
         <v>9</v>
       </c>
       <c r="B246" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C246" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="D246" t="s">
         <v>990</v>
@@ -7557,10 +7557,10 @@
         <v>9</v>
       </c>
       <c r="B247" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C247" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="D247" t="s">
         <v>991</v>
@@ -7574,10 +7574,10 @@
         <v>9</v>
       </c>
       <c r="B248" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C248" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="D248" t="s">
         <v>992</v>
@@ -7591,10 +7591,10 @@
         <v>9</v>
       </c>
       <c r="B249" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C249" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="D249" t="s">
         <v>993</v>
@@ -7608,10 +7608,10 @@
         <v>9</v>
       </c>
       <c r="B250" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C250" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="D250" t="s">
         <v>994</v>
@@ -7625,10 +7625,10 @@
         <v>9</v>
       </c>
       <c r="B251" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C251" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="D251" t="s">
         <v>994</v>
@@ -7642,10 +7642,10 @@
         <v>10</v>
       </c>
       <c r="B252" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C252" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="D252" t="s">
         <v>995</v>
@@ -7659,10 +7659,10 @@
         <v>10</v>
       </c>
       <c r="B253" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C253" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="E253" t="s">
         <v>1064</v>
@@ -7673,10 +7673,10 @@
         <v>10</v>
       </c>
       <c r="B254" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C254" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="D254" t="s">
         <v>996</v>
@@ -7690,10 +7690,10 @@
         <v>10</v>
       </c>
       <c r="B255" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C255" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="D255" t="s">
         <v>997</v>
@@ -7707,10 +7707,10 @@
         <v>10</v>
       </c>
       <c r="B256" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C256" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="D256" t="s">
         <v>998</v>
@@ -7724,10 +7724,10 @@
         <v>10</v>
       </c>
       <c r="B257" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C257" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="D257" t="s">
         <v>999</v>
@@ -7741,10 +7741,10 @@
         <v>10</v>
       </c>
       <c r="B258" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C258" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="D258" t="s">
         <v>1000</v>
@@ -7758,10 +7758,10 @@
         <v>10</v>
       </c>
       <c r="B259" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C259" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="E259" t="s">
         <v>1062</v>
@@ -7772,10 +7772,10 @@
         <v>10</v>
       </c>
       <c r="B260" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C260" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="D260" t="s">
         <v>1001</v>
@@ -7789,10 +7789,10 @@
         <v>10</v>
       </c>
       <c r="B261" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C261" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="D261" t="s">
         <v>1002</v>
@@ -7806,10 +7806,10 @@
         <v>10</v>
       </c>
       <c r="B262" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C262" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="D262" t="s">
         <v>1003</v>
@@ -7823,10 +7823,10 @@
         <v>10</v>
       </c>
       <c r="B263" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C263" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="D263" t="s">
         <v>1004</v>
@@ -7840,10 +7840,10 @@
         <v>10</v>
       </c>
       <c r="B264" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C264" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="D264" t="s">
         <v>1005</v>
@@ -7857,10 +7857,10 @@
         <v>10</v>
       </c>
       <c r="B265" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C265" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="D265" t="s">
         <v>1006</v>
@@ -7874,10 +7874,10 @@
         <v>10</v>
       </c>
       <c r="B266" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C266" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="D266" t="s">
         <v>1007</v>
@@ -7891,10 +7891,10 @@
         <v>10</v>
       </c>
       <c r="B267" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C267" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="D267" t="s">
         <v>1008</v>
@@ -7908,10 +7908,10 @@
         <v>10</v>
       </c>
       <c r="B268" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C268" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="D268" t="s">
         <v>1009</v>
@@ -7925,10 +7925,10 @@
         <v>10</v>
       </c>
       <c r="B269" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C269" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="E269" t="s">
         <v>1062</v>
@@ -7939,10 +7939,10 @@
         <v>10</v>
       </c>
       <c r="B270" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C270" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="E270" t="s">
         <v>1064</v>
@@ -7953,10 +7953,10 @@
         <v>10</v>
       </c>
       <c r="B271" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C271" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="D271" t="s">
         <v>1010</v>
@@ -7970,10 +7970,10 @@
         <v>10</v>
       </c>
       <c r="B272" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C272" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="E272" t="s">
         <v>1062</v>
@@ -7984,10 +7984,10 @@
         <v>10</v>
       </c>
       <c r="B273" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C273" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="D273" t="s">
         <v>1011</v>
@@ -8001,10 +8001,10 @@
         <v>10</v>
       </c>
       <c r="B274" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C274" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="D274" t="s">
         <v>1012</v>
@@ -8018,10 +8018,10 @@
         <v>10</v>
       </c>
       <c r="B275" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C275" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="D275" t="s">
         <v>1013</v>
@@ -8035,10 +8035,10 @@
         <v>10</v>
       </c>
       <c r="B276" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C276" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="D276" t="s">
         <v>1014</v>
@@ -8052,10 +8052,10 @@
         <v>10</v>
       </c>
       <c r="B277" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C277" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="D277" t="s">
         <v>1015</v>
@@ -8069,13 +8069,13 @@
         <v>10</v>
       </c>
       <c r="B278" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C278" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="D278" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="E278" t="s">
         <v>1063</v>
@@ -8086,10 +8086,10 @@
         <v>10</v>
       </c>
       <c r="B279" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C279" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="D279" t="s">
         <v>1016</v>
@@ -8103,10 +8103,10 @@
         <v>10</v>
       </c>
       <c r="B280" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C280" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="D280" t="s">
         <v>1017</v>
@@ -8120,10 +8120,10 @@
         <v>10</v>
       </c>
       <c r="B281" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C281" t="s">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="D281" t="s">
         <v>1018</v>
@@ -8137,10 +8137,10 @@
         <v>10</v>
       </c>
       <c r="B282" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C282" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="D282" t="s">
         <v>1019</v>
@@ -8154,10 +8154,10 @@
         <v>10</v>
       </c>
       <c r="B283" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C283" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D283" t="s">
         <v>1020</v>
@@ -8171,10 +8171,10 @@
         <v>10</v>
       </c>
       <c r="B284" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C284" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="D284" t="s">
         <v>1021</v>
@@ -8188,10 +8188,10 @@
         <v>10</v>
       </c>
       <c r="B285" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C285" t="s">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="D285" t="s">
         <v>1022</v>
@@ -8205,10 +8205,10 @@
         <v>10</v>
       </c>
       <c r="B286" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C286" t="s">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="D286" t="s">
         <v>1023</v>
@@ -8222,10 +8222,10 @@
         <v>10</v>
       </c>
       <c r="B287" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C287" t="s">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="D287" t="s">
         <v>1024</v>
@@ -8239,10 +8239,10 @@
         <v>10</v>
       </c>
       <c r="B288" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C288" t="s">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="D288" t="s">
         <v>1025</v>
@@ -8256,10 +8256,10 @@
         <v>10</v>
       </c>
       <c r="B289" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C289" t="s">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="D289" t="s">
         <v>1026</v>
@@ -8273,10 +8273,10 @@
         <v>10</v>
       </c>
       <c r="B290" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C290" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="D290" t="s">
         <v>1027</v>
@@ -8290,10 +8290,10 @@
         <v>10</v>
       </c>
       <c r="B291" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C291" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="D291" t="s">
         <v>1028</v>
@@ -8307,10 +8307,10 @@
         <v>10</v>
       </c>
       <c r="B292" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C292" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="D292" t="s">
         <v>1029</v>
@@ -8324,10 +8324,10 @@
         <v>10</v>
       </c>
       <c r="B293" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C293" t="s">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="D293" t="s">
         <v>1030</v>
@@ -8341,10 +8341,10 @@
         <v>10</v>
       </c>
       <c r="B294" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C294" t="s">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="D294" t="s">
         <v>1031</v>
@@ -8358,10 +8358,10 @@
         <v>10</v>
       </c>
       <c r="B295" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C295" t="s">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="D295" t="s">
         <v>1032</v>
@@ -8375,10 +8375,10 @@
         <v>10</v>
       </c>
       <c r="B296" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C296" t="s">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="D296" t="s">
         <v>1033</v>
@@ -8392,10 +8392,10 @@
         <v>10</v>
       </c>
       <c r="B297" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C297" t="s">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="D297" t="s">
         <v>1034</v>
@@ -8409,10 +8409,10 @@
         <v>10</v>
       </c>
       <c r="B298" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C298" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="D298" t="s">
         <v>1035</v>
@@ -8426,10 +8426,10 @@
         <v>10</v>
       </c>
       <c r="B299" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C299" t="s">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="D299" t="s">
         <v>1036</v>
@@ -8443,10 +8443,10 @@
         <v>10</v>
       </c>
       <c r="B300" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C300" t="s">
-        <v>730</v>
+        <v>732</v>
       </c>
       <c r="D300" t="s">
         <v>1037</v>
@@ -8460,10 +8460,10 @@
         <v>10</v>
       </c>
       <c r="B301" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C301" t="s">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="D301" t="s">
         <v>1038</v>
@@ -8477,10 +8477,10 @@
         <v>11</v>
       </c>
       <c r="B302" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C302" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="E302" t="s">
         <v>1062</v>
@@ -8491,10 +8491,10 @@
         <v>11</v>
       </c>
       <c r="B303" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C303" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="E303" t="s">
         <v>1062</v>
@@ -8505,10 +8505,10 @@
         <v>11</v>
       </c>
       <c r="B304" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C304" t="s">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="E304" t="s">
         <v>1062</v>
@@ -8519,10 +8519,10 @@
         <v>11</v>
       </c>
       <c r="B305" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C305" t="s">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="E305" t="s">
         <v>1062</v>
@@ -8533,10 +8533,10 @@
         <v>11</v>
       </c>
       <c r="B306" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C306" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="E306" t="s">
         <v>1062</v>
@@ -8547,10 +8547,10 @@
         <v>11</v>
       </c>
       <c r="B307" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C307" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="E307" t="s">
         <v>1062</v>
@@ -8561,10 +8561,10 @@
         <v>11</v>
       </c>
       <c r="B308" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C308" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="E308" t="s">
         <v>1062</v>
@@ -8575,10 +8575,10 @@
         <v>11</v>
       </c>
       <c r="B309" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C309" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="E309" t="s">
         <v>1062</v>
@@ -8589,10 +8589,10 @@
         <v>11</v>
       </c>
       <c r="B310" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C310" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="E310" t="s">
         <v>1062</v>
@@ -8603,10 +8603,10 @@
         <v>11</v>
       </c>
       <c r="B311" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C311" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="E311" t="s">
         <v>1062</v>
@@ -8617,10 +8617,10 @@
         <v>11</v>
       </c>
       <c r="B312" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C312" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="E312" t="s">
         <v>1062</v>
@@ -8631,10 +8631,10 @@
         <v>11</v>
       </c>
       <c r="B313" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C313" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="E313" t="s">
         <v>1062</v>
@@ -8645,10 +8645,10 @@
         <v>11</v>
       </c>
       <c r="B314" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C314" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="E314" t="s">
         <v>1062</v>
@@ -8659,10 +8659,10 @@
         <v>11</v>
       </c>
       <c r="B315" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C315" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="E315" t="s">
         <v>1062</v>
@@ -8673,10 +8673,10 @@
         <v>11</v>
       </c>
       <c r="B316" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C316" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="E316" t="s">
         <v>1062</v>
@@ -8687,10 +8687,10 @@
         <v>11</v>
       </c>
       <c r="B317" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C317" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="E317" t="s">
         <v>1062</v>
@@ -8701,10 +8701,10 @@
         <v>11</v>
       </c>
       <c r="B318" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C318" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="E318" t="s">
         <v>1062</v>
@@ -8715,10 +8715,10 @@
         <v>11</v>
       </c>
       <c r="B319" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C319" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="E319" t="s">
         <v>1062</v>
@@ -8729,10 +8729,10 @@
         <v>11</v>
       </c>
       <c r="B320" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C320" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="E320" t="s">
         <v>1062</v>
@@ -8743,10 +8743,10 @@
         <v>11</v>
       </c>
       <c r="B321" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C321" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="E321" t="s">
         <v>1062</v>
@@ -8757,10 +8757,10 @@
         <v>11</v>
       </c>
       <c r="B322" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C322" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="E322" t="s">
         <v>1062</v>
@@ -8771,10 +8771,10 @@
         <v>11</v>
       </c>
       <c r="B323" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C323" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="E323" t="s">
         <v>1062</v>
@@ -8785,10 +8785,10 @@
         <v>11</v>
       </c>
       <c r="B324" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C324" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="E324" t="s">
         <v>1062</v>
@@ -8799,10 +8799,10 @@
         <v>11</v>
       </c>
       <c r="B325" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C325" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="E325" t="s">
         <v>1062</v>
@@ -8813,10 +8813,10 @@
         <v>11</v>
       </c>
       <c r="B326" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C326" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="E326" t="s">
         <v>1062</v>
@@ -8827,10 +8827,10 @@
         <v>11</v>
       </c>
       <c r="B327" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C327" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="E327" t="s">
         <v>1062</v>
@@ -8841,10 +8841,10 @@
         <v>11</v>
       </c>
       <c r="B328" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C328" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="E328" t="s">
         <v>1062</v>
@@ -8855,10 +8855,10 @@
         <v>11</v>
       </c>
       <c r="B329" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C329" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="E329" t="s">
         <v>1062</v>
@@ -8869,10 +8869,10 @@
         <v>11</v>
       </c>
       <c r="B330" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C330" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="E330" t="s">
         <v>1062</v>
@@ -8883,10 +8883,10 @@
         <v>11</v>
       </c>
       <c r="B331" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C331" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="E331" t="s">
         <v>1062</v>
@@ -8897,10 +8897,10 @@
         <v>11</v>
       </c>
       <c r="B332" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C332" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="E332" t="s">
         <v>1062</v>
@@ -8911,10 +8911,10 @@
         <v>11</v>
       </c>
       <c r="B333" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C333" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="E333" t="s">
         <v>1062</v>
@@ -8925,10 +8925,10 @@
         <v>11</v>
       </c>
       <c r="B334" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C334" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="E334" t="s">
         <v>1062</v>
@@ -8939,10 +8939,10 @@
         <v>11</v>
       </c>
       <c r="B335" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C335" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="E335" t="s">
         <v>1062</v>
@@ -8953,10 +8953,10 @@
         <v>11</v>
       </c>
       <c r="B336" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C336" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="E336" t="s">
         <v>1062</v>
@@ -8967,10 +8967,10 @@
         <v>11</v>
       </c>
       <c r="B337" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C337" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="E337" t="s">
         <v>1062</v>
@@ -8981,10 +8981,10 @@
         <v>11</v>
       </c>
       <c r="B338" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C338" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="E338" t="s">
         <v>1062</v>
@@ -8995,10 +8995,10 @@
         <v>11</v>
       </c>
       <c r="B339" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C339" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="E339" t="s">
         <v>1062</v>
@@ -9009,10 +9009,10 @@
         <v>11</v>
       </c>
       <c r="B340" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C340" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="E340" t="s">
         <v>1062</v>
@@ -9023,10 +9023,10 @@
         <v>11</v>
       </c>
       <c r="B341" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C341" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="E341" t="s">
         <v>1062</v>
@@ -9037,10 +9037,10 @@
         <v>11</v>
       </c>
       <c r="B342" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C342" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="E342" t="s">
         <v>1062</v>
@@ -9051,10 +9051,10 @@
         <v>11</v>
       </c>
       <c r="B343" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C343" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="E343" t="s">
         <v>1062</v>
@@ -9065,10 +9065,10 @@
         <v>11</v>
       </c>
       <c r="B344" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C344" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="E344" t="s">
         <v>1062</v>
@@ -9079,10 +9079,10 @@
         <v>11</v>
       </c>
       <c r="B345" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C345" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="E345" t="s">
         <v>1062</v>
@@ -9093,10 +9093,10 @@
         <v>11</v>
       </c>
       <c r="B346" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C346" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="E346" t="s">
         <v>1062</v>
@@ -9107,10 +9107,10 @@
         <v>11</v>
       </c>
       <c r="B347" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C347" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="E347" t="s">
         <v>1062</v>
@@ -9121,10 +9121,10 @@
         <v>11</v>
       </c>
       <c r="B348" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C348" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="E348" t="s">
         <v>1062</v>
@@ -9135,10 +9135,10 @@
         <v>11</v>
       </c>
       <c r="B349" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C349" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="E349" t="s">
         <v>1062</v>
@@ -9149,10 +9149,10 @@
         <v>11</v>
       </c>
       <c r="B350" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C350" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="E350" t="s">
         <v>1062</v>
@@ -9163,10 +9163,10 @@
         <v>11</v>
       </c>
       <c r="B351" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C351" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="E351" t="s">
         <v>1062</v>
@@ -9180,7 +9180,7 @@
         <v>17</v>
       </c>
       <c r="C352" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="E352" t="s">
         <v>1062</v>
@@ -9194,7 +9194,7 @@
         <v>28</v>
       </c>
       <c r="C353" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="E353" t="s">
         <v>1064</v>
@@ -9208,7 +9208,7 @@
         <v>45</v>
       </c>
       <c r="C354" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="E354" t="s">
         <v>1064</v>
@@ -9222,7 +9222,7 @@
         <v>46</v>
       </c>
       <c r="C355" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="E355" t="s">
         <v>1064</v>
@@ -9233,10 +9233,10 @@
         <v>12</v>
       </c>
       <c r="B356" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C356" t="s">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="E356" t="s">
         <v>1064</v>
@@ -9247,10 +9247,10 @@
         <v>12</v>
       </c>
       <c r="B357" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C357" t="s">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="E357" t="s">
         <v>1064</v>
@@ -9261,10 +9261,10 @@
         <v>12</v>
       </c>
       <c r="B358" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C358" t="s">
-        <v>737</v>
+        <v>739</v>
       </c>
       <c r="E358" t="s">
         <v>1064</v>
@@ -9275,10 +9275,10 @@
         <v>12</v>
       </c>
       <c r="B359" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C359" t="s">
-        <v>737</v>
+        <v>739</v>
       </c>
       <c r="E359" t="s">
         <v>1064</v>
@@ -9289,10 +9289,10 @@
         <v>12</v>
       </c>
       <c r="B360" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C360" t="s">
-        <v>738</v>
+        <v>740</v>
       </c>
       <c r="E360" t="s">
         <v>1064</v>
@@ -9303,10 +9303,10 @@
         <v>12</v>
       </c>
       <c r="B361" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C361" t="s">
-        <v>739</v>
+        <v>741</v>
       </c>
       <c r="E361" t="s">
         <v>1064</v>
@@ -9317,10 +9317,10 @@
         <v>12</v>
       </c>
       <c r="B362" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C362" t="s">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="E362" t="s">
         <v>1064</v>
@@ -9331,10 +9331,10 @@
         <v>12</v>
       </c>
       <c r="B363" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C363" t="s">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="E363" t="s">
         <v>1064</v>
@@ -9345,10 +9345,10 @@
         <v>12</v>
       </c>
       <c r="B364" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C364" t="s">
-        <v>742</v>
+        <v>744</v>
       </c>
       <c r="E364" t="s">
         <v>1064</v>
@@ -9359,10 +9359,10 @@
         <v>12</v>
       </c>
       <c r="B365" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C365" t="s">
-        <v>743</v>
+        <v>745</v>
       </c>
       <c r="E365" t="s">
         <v>1064</v>
@@ -9373,10 +9373,10 @@
         <v>12</v>
       </c>
       <c r="B366" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C366" t="s">
-        <v>744</v>
+        <v>746</v>
       </c>
       <c r="E366" t="s">
         <v>1064</v>
@@ -9387,10 +9387,10 @@
         <v>12</v>
       </c>
       <c r="B367" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C367" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
       <c r="E367" t="s">
         <v>1064</v>
@@ -9401,10 +9401,10 @@
         <v>12</v>
       </c>
       <c r="B368" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C368" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="E368" t="s">
         <v>1064</v>
@@ -9415,7 +9415,7 @@
         <v>12</v>
       </c>
       <c r="B369" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C369" t="s">
         <v>747</v>
@@ -9429,16 +9429,13 @@
         <v>12</v>
       </c>
       <c r="B370" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C370" t="s">
         <v>748</v>
       </c>
-      <c r="D370" t="s">
-        <v>748</v>
-      </c>
       <c r="E370" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="371" spans="1:5">
@@ -9446,7 +9443,7 @@
         <v>12</v>
       </c>
       <c r="B371" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C371" t="s">
         <v>749</v>
@@ -9460,10 +9457,10 @@
         <v>12</v>
       </c>
       <c r="B372" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C372" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="E372" t="s">
         <v>1064</v>
@@ -9474,13 +9471,16 @@
         <v>12</v>
       </c>
       <c r="B373" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C373" t="s">
-        <v>750</v>
+        <v>751</v>
+      </c>
+      <c r="D373" t="s">
+        <v>751</v>
       </c>
       <c r="E373" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="374" spans="1:5">
@@ -9488,10 +9488,10 @@
         <v>12</v>
       </c>
       <c r="B374" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C374" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="E374" t="s">
         <v>1064</v>
@@ -9502,16 +9502,13 @@
         <v>12</v>
       </c>
       <c r="B375" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C375" t="s">
         <v>752</v>
       </c>
-      <c r="D375" t="s">
-        <v>752</v>
-      </c>
       <c r="E375" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="376" spans="1:5">
@@ -9519,7 +9516,7 @@
         <v>12</v>
       </c>
       <c r="B376" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C376" t="s">
         <v>753</v>
@@ -9533,7 +9530,7 @@
         <v>12</v>
       </c>
       <c r="B377" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C377" t="s">
         <v>754</v>
@@ -9547,13 +9544,16 @@
         <v>12</v>
       </c>
       <c r="B378" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C378" t="s">
         <v>755</v>
       </c>
+      <c r="D378" t="s">
+        <v>755</v>
+      </c>
       <c r="E378" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="379" spans="1:5">
@@ -9561,16 +9561,13 @@
         <v>12</v>
       </c>
       <c r="B379" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C379" t="s">
         <v>756</v>
       </c>
-      <c r="D379" t="s">
-        <v>756</v>
-      </c>
       <c r="E379" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="380" spans="1:5">
@@ -9578,16 +9575,13 @@
         <v>12</v>
       </c>
       <c r="B380" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C380" t="s">
         <v>757</v>
       </c>
-      <c r="D380" t="s">
-        <v>757</v>
-      </c>
       <c r="E380" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="381" spans="1:5">
@@ -9595,7 +9589,7 @@
         <v>12</v>
       </c>
       <c r="B381" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C381" t="s">
         <v>758</v>
@@ -9609,13 +9603,16 @@
         <v>12</v>
       </c>
       <c r="B382" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C382" t="s">
         <v>759</v>
       </c>
+      <c r="D382" t="s">
+        <v>759</v>
+      </c>
       <c r="E382" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="383" spans="1:5">
@@ -9623,13 +9620,16 @@
         <v>12</v>
       </c>
       <c r="B383" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C383" t="s">
         <v>760</v>
       </c>
+      <c r="D383" t="s">
+        <v>760</v>
+      </c>
       <c r="E383" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="384" spans="1:5">
@@ -9637,10 +9637,10 @@
         <v>12</v>
       </c>
       <c r="B384" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C384" t="s">
-        <v>761</v>
+        <v>746</v>
       </c>
       <c r="E384" t="s">
         <v>1064</v>
@@ -9651,10 +9651,10 @@
         <v>12</v>
       </c>
       <c r="B385" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C385" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="E385" t="s">
         <v>1064</v>
@@ -9665,10 +9665,10 @@
         <v>12</v>
       </c>
       <c r="B386" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C386" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="E386" t="s">
         <v>1064</v>
@@ -9679,7 +9679,7 @@
         <v>12</v>
       </c>
       <c r="B387" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C387" t="s">
         <v>763</v>
@@ -9693,7 +9693,7 @@
         <v>12</v>
       </c>
       <c r="B388" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C388" t="s">
         <v>764</v>
@@ -9707,10 +9707,10 @@
         <v>12</v>
       </c>
       <c r="B389" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C389" t="s">
-        <v>744</v>
+        <v>765</v>
       </c>
       <c r="E389" t="s">
         <v>1064</v>
@@ -9721,7 +9721,7 @@
         <v>12</v>
       </c>
       <c r="B390" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C390" t="s">
         <v>765</v>
@@ -9735,7 +9735,7 @@
         <v>12</v>
       </c>
       <c r="B391" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C391" t="s">
         <v>766</v>
@@ -9749,10 +9749,10 @@
         <v>12</v>
       </c>
       <c r="B392" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C392" t="s">
-        <v>767</v>
+        <v>747</v>
       </c>
       <c r="E392" t="s">
         <v>1064</v>
@@ -9763,10 +9763,10 @@
         <v>12</v>
       </c>
       <c r="B393" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C393" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="E393" t="s">
         <v>1064</v>
@@ -9777,16 +9777,13 @@
         <v>12</v>
       </c>
       <c r="B394" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C394" t="s">
-        <v>757</v>
-      </c>
-      <c r="D394" t="s">
-        <v>757</v>
+        <v>768</v>
       </c>
       <c r="E394" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="395" spans="1:5">
@@ -9794,7 +9791,7 @@
         <v>12</v>
       </c>
       <c r="B395" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C395" t="s">
         <v>769</v>
@@ -9808,7 +9805,7 @@
         <v>12</v>
       </c>
       <c r="B396" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C396" t="s">
         <v>770</v>
@@ -9822,13 +9819,16 @@
         <v>12</v>
       </c>
       <c r="B397" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C397" t="s">
-        <v>477</v>
+        <v>760</v>
+      </c>
+      <c r="D397" t="s">
+        <v>760</v>
       </c>
       <c r="E397" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="398" spans="1:5">
@@ -9836,10 +9836,10 @@
         <v>12</v>
       </c>
       <c r="B398" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C398" t="s">
-        <v>494</v>
+        <v>771</v>
       </c>
       <c r="E398" t="s">
         <v>1064</v>
@@ -9850,10 +9850,10 @@
         <v>12</v>
       </c>
       <c r="B399" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C399" t="s">
-        <v>477</v>
+        <v>772</v>
       </c>
       <c r="E399" t="s">
         <v>1064</v>
@@ -9864,10 +9864,10 @@
         <v>12</v>
       </c>
       <c r="B400" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C400" t="s">
-        <v>771</v>
+        <v>478</v>
       </c>
       <c r="E400" t="s">
         <v>1064</v>
@@ -9878,10 +9878,10 @@
         <v>12</v>
       </c>
       <c r="B401" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C401" t="s">
-        <v>772</v>
+        <v>495</v>
       </c>
       <c r="E401" t="s">
         <v>1064</v>
@@ -9892,7 +9892,7 @@
         <v>13</v>
       </c>
       <c r="B402" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C402" t="s">
         <v>773</v>
@@ -9906,7 +9906,7 @@
         <v>13</v>
       </c>
       <c r="B403" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C403" t="s">
         <v>774</v>
@@ -9920,7 +9920,7 @@
         <v>13</v>
       </c>
       <c r="B404" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C404" t="s">
         <v>775</v>
@@ -9934,10 +9934,10 @@
         <v>13</v>
       </c>
       <c r="B405" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C405" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="D405" t="s">
         <v>969</v>
@@ -9951,10 +9951,10 @@
         <v>13</v>
       </c>
       <c r="B406" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C406" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="D406" t="s">
         <v>953</v>
@@ -9968,10 +9968,10 @@
         <v>13</v>
       </c>
       <c r="B407" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C407" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="D407" t="s">
         <v>975</v>
@@ -9985,10 +9985,10 @@
         <v>13</v>
       </c>
       <c r="B408" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C408" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="D408" t="s">
         <v>976</v>
@@ -10002,7 +10002,7 @@
         <v>13</v>
       </c>
       <c r="B409" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C409" t="s">
         <v>776</v>
@@ -10019,7 +10019,7 @@
         <v>13</v>
       </c>
       <c r="B410" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C410" t="s">
         <v>777</v>
@@ -10033,7 +10033,7 @@
         <v>13</v>
       </c>
       <c r="B411" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C411" t="s">
         <v>778</v>
@@ -10050,7 +10050,7 @@
         <v>13</v>
       </c>
       <c r="B412" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C412" t="s">
         <v>778</v>
@@ -10067,7 +10067,7 @@
         <v>13</v>
       </c>
       <c r="B413" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C413" t="s">
         <v>778</v>
@@ -10084,7 +10084,7 @@
         <v>13</v>
       </c>
       <c r="B414" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C414" t="s">
         <v>778</v>
@@ -10101,7 +10101,7 @@
         <v>13</v>
       </c>
       <c r="B415" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C415" t="s">
         <v>778</v>
@@ -10118,7 +10118,7 @@
         <v>13</v>
       </c>
       <c r="B416" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C416" t="s">
         <v>778</v>
@@ -10135,7 +10135,7 @@
         <v>13</v>
       </c>
       <c r="B417" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C417" t="s">
         <v>778</v>
@@ -10152,7 +10152,7 @@
         <v>13</v>
       </c>
       <c r="B418" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C418" t="s">
         <v>778</v>
@@ -10169,7 +10169,7 @@
         <v>13</v>
       </c>
       <c r="B419" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C419" t="s">
         <v>778</v>
@@ -10186,7 +10186,7 @@
         <v>13</v>
       </c>
       <c r="B420" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C420" t="s">
         <v>778</v>
@@ -10203,7 +10203,7 @@
         <v>13</v>
       </c>
       <c r="B421" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C421" t="s">
         <v>778</v>
@@ -10220,7 +10220,7 @@
         <v>13</v>
       </c>
       <c r="B422" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C422" t="s">
         <v>778</v>
@@ -10237,7 +10237,7 @@
         <v>13</v>
       </c>
       <c r="B423" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C423" t="s">
         <v>778</v>
@@ -10254,7 +10254,7 @@
         <v>13</v>
       </c>
       <c r="B424" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C424" t="s">
         <v>779</v>
@@ -10271,7 +10271,7 @@
         <v>13</v>
       </c>
       <c r="B425" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C425" t="s">
         <v>780</v>
@@ -10288,7 +10288,7 @@
         <v>13</v>
       </c>
       <c r="B426" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C426" t="s">
         <v>781</v>
@@ -10305,7 +10305,7 @@
         <v>13</v>
       </c>
       <c r="B427" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C427" t="s">
         <v>782</v>
@@ -10322,7 +10322,7 @@
         <v>13</v>
       </c>
       <c r="B428" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C428" t="s">
         <v>783</v>
@@ -10336,7 +10336,7 @@
         <v>13</v>
       </c>
       <c r="B429" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C429" t="s">
         <v>784</v>
@@ -10350,7 +10350,7 @@
         <v>13</v>
       </c>
       <c r="B430" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C430" t="s">
         <v>785</v>
@@ -10367,7 +10367,7 @@
         <v>13</v>
       </c>
       <c r="B431" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C431" t="s">
         <v>786</v>
@@ -10384,7 +10384,7 @@
         <v>13</v>
       </c>
       <c r="B432" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C432" t="s">
         <v>787</v>
@@ -10398,7 +10398,7 @@
         <v>13</v>
       </c>
       <c r="B433" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C433" t="s">
         <v>788</v>
@@ -10415,7 +10415,7 @@
         <v>13</v>
       </c>
       <c r="B434" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C434" t="s">
         <v>789</v>
@@ -10432,7 +10432,7 @@
         <v>13</v>
       </c>
       <c r="B435" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C435" t="s">
         <v>790</v>
@@ -10449,7 +10449,7 @@
         <v>13</v>
       </c>
       <c r="B436" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C436" t="s">
         <v>791</v>
@@ -10466,7 +10466,7 @@
         <v>13</v>
       </c>
       <c r="B437" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C437" t="s">
         <v>792</v>
@@ -10483,7 +10483,7 @@
         <v>13</v>
       </c>
       <c r="B438" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C438" t="s">
         <v>793</v>
@@ -10500,7 +10500,7 @@
         <v>13</v>
       </c>
       <c r="B439" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C439" t="s">
         <v>794</v>
@@ -10517,7 +10517,7 @@
         <v>13</v>
       </c>
       <c r="B440" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C440" t="s">
         <v>795</v>
@@ -10534,7 +10534,7 @@
         <v>13</v>
       </c>
       <c r="B441" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C441" t="s">
         <v>796</v>
@@ -10551,7 +10551,7 @@
         <v>13</v>
       </c>
       <c r="B442" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C442" t="s">
         <v>797</v>
@@ -10568,7 +10568,7 @@
         <v>13</v>
       </c>
       <c r="B443" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C443" t="s">
         <v>798</v>
@@ -10585,7 +10585,7 @@
         <v>13</v>
       </c>
       <c r="B444" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C444" t="s">
         <v>799</v>
@@ -10599,7 +10599,7 @@
         <v>13</v>
       </c>
       <c r="B445" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C445" t="s">
         <v>799</v>
@@ -10613,7 +10613,7 @@
         <v>13</v>
       </c>
       <c r="B446" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C446" t="s">
         <v>800</v>
@@ -10630,7 +10630,7 @@
         <v>13</v>
       </c>
       <c r="B447" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C447" t="s">
         <v>801</v>
@@ -10647,7 +10647,7 @@
         <v>13</v>
       </c>
       <c r="B448" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C448" t="s">
         <v>802</v>
@@ -10661,7 +10661,7 @@
         <v>13</v>
       </c>
       <c r="B449" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C449" t="s">
         <v>803</v>
@@ -10678,7 +10678,7 @@
         <v>13</v>
       </c>
       <c r="B450" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C450" t="s">
         <v>804</v>
@@ -10692,7 +10692,7 @@
         <v>13</v>
       </c>
       <c r="B451" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C451" t="s">
         <v>805</v>
@@ -10706,10 +10706,10 @@
         <v>14</v>
       </c>
       <c r="B452" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C452" s="1" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="D452" t="s">
         <v>968</v>
@@ -10723,10 +10723,10 @@
         <v>14</v>
       </c>
       <c r="B453" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C453" s="1" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="E453" t="s">
         <v>1062</v>
@@ -10737,10 +10737,10 @@
         <v>14</v>
       </c>
       <c r="B454" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C454" s="1" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="E454" t="s">
         <v>1062</v>
@@ -10751,10 +10751,10 @@
         <v>14</v>
       </c>
       <c r="B455" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C455" s="1" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="E455" t="s">
         <v>1062</v>
@@ -10765,10 +10765,10 @@
         <v>14</v>
       </c>
       <c r="B456" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C456" s="1" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="E456" t="s">
         <v>1062</v>
@@ -10779,10 +10779,10 @@
         <v>14</v>
       </c>
       <c r="B457" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C457" s="1" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="E457" t="s">
         <v>1062</v>
@@ -10793,10 +10793,10 @@
         <v>14</v>
       </c>
       <c r="B458" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C458" s="1" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="E458" t="s">
         <v>1062</v>
@@ -10807,10 +10807,10 @@
         <v>14</v>
       </c>
       <c r="B459" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C459" s="1" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="E459" t="s">
         <v>1062</v>
@@ -10821,10 +10821,10 @@
         <v>14</v>
       </c>
       <c r="B460" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C460" s="1" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="E460" t="s">
         <v>1062</v>
@@ -10835,7 +10835,7 @@
         <v>14</v>
       </c>
       <c r="B461" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C461" t="s">
         <v>776</v>
@@ -10852,7 +10852,7 @@
         <v>14</v>
       </c>
       <c r="B462" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C462" s="1" t="s">
         <v>806</v>
@@ -10866,7 +10866,7 @@
         <v>14</v>
       </c>
       <c r="B463" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C463" s="1" t="s">
         <v>807</v>
@@ -10880,7 +10880,7 @@
         <v>14</v>
       </c>
       <c r="B464" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C464" s="1" t="s">
         <v>808</v>
@@ -10894,7 +10894,7 @@
         <v>14</v>
       </c>
       <c r="B465" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C465" s="1" t="s">
         <v>809</v>
@@ -10908,7 +10908,7 @@
         <v>14</v>
       </c>
       <c r="B466" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C466" s="1" t="s">
         <v>810</v>
@@ -10922,7 +10922,7 @@
         <v>14</v>
       </c>
       <c r="B467" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C467" s="1" t="s">
         <v>811</v>
@@ -10936,7 +10936,7 @@
         <v>14</v>
       </c>
       <c r="B468" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C468" s="1" t="s">
         <v>812</v>
@@ -10950,7 +10950,7 @@
         <v>14</v>
       </c>
       <c r="B469" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C469" s="1" t="s">
         <v>813</v>
@@ -10964,7 +10964,7 @@
         <v>14</v>
       </c>
       <c r="B470" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C470" s="1" t="s">
         <v>814</v>
@@ -10978,7 +10978,7 @@
         <v>14</v>
       </c>
       <c r="B471" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C471" s="1" t="s">
         <v>815</v>
@@ -10992,7 +10992,7 @@
         <v>14</v>
       </c>
       <c r="B472" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C472" s="1" t="s">
         <v>816</v>
@@ -11006,7 +11006,7 @@
         <v>14</v>
       </c>
       <c r="B473" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C473" s="1" t="s">
         <v>817</v>
@@ -11020,7 +11020,7 @@
         <v>14</v>
       </c>
       <c r="B474" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C474" s="1" t="s">
         <v>818</v>
@@ -11034,7 +11034,7 @@
         <v>14</v>
       </c>
       <c r="B475" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C475" s="1" t="s">
         <v>819</v>
@@ -11048,7 +11048,7 @@
         <v>14</v>
       </c>
       <c r="B476" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C476" s="1" t="s">
         <v>820</v>
@@ -11062,7 +11062,7 @@
         <v>14</v>
       </c>
       <c r="B477" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C477" s="1" t="s">
         <v>821</v>
@@ -11076,7 +11076,7 @@
         <v>14</v>
       </c>
       <c r="B478" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C478" s="1" t="s">
         <v>822</v>
@@ -11090,7 +11090,7 @@
         <v>14</v>
       </c>
       <c r="B479" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C479" s="1" t="s">
         <v>823</v>
@@ -11104,7 +11104,7 @@
         <v>14</v>
       </c>
       <c r="B480" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C480" t="s">
         <v>824</v>
@@ -11121,7 +11121,7 @@
         <v>14</v>
       </c>
       <c r="B481" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C481" s="1" t="s">
         <v>825</v>
@@ -11138,7 +11138,7 @@
         <v>14</v>
       </c>
       <c r="B482" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C482" s="1" t="s">
         <v>826</v>
@@ -11152,7 +11152,7 @@
         <v>14</v>
       </c>
       <c r="B483" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C483" s="1" t="s">
         <v>827</v>
@@ -11166,7 +11166,7 @@
         <v>14</v>
       </c>
       <c r="B484" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C484" s="1" t="s">
         <v>828</v>
@@ -11180,7 +11180,7 @@
         <v>14</v>
       </c>
       <c r="B485" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C485" s="1" t="s">
         <v>829</v>
@@ -11194,7 +11194,7 @@
         <v>14</v>
       </c>
       <c r="B486" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C486" s="1" t="s">
         <v>830</v>
@@ -11208,7 +11208,7 @@
         <v>14</v>
       </c>
       <c r="B487" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C487" s="1" t="s">
         <v>831</v>
@@ -11222,7 +11222,7 @@
         <v>14</v>
       </c>
       <c r="B488" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C488" s="1" t="s">
         <v>832</v>
@@ -11236,7 +11236,7 @@
         <v>14</v>
       </c>
       <c r="B489" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C489" s="1" t="s">
         <v>833</v>
@@ -11250,7 +11250,7 @@
         <v>14</v>
       </c>
       <c r="B490" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C490" s="1" t="s">
         <v>834</v>
@@ -11264,7 +11264,7 @@
         <v>14</v>
       </c>
       <c r="B491" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C491" s="1" t="s">
         <v>835</v>
@@ -11278,7 +11278,7 @@
         <v>14</v>
       </c>
       <c r="B492" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C492" s="1" t="s">
         <v>836</v>
@@ -11292,7 +11292,7 @@
         <v>14</v>
       </c>
       <c r="B493" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C493" s="1" t="s">
         <v>837</v>
@@ -11306,7 +11306,7 @@
         <v>14</v>
       </c>
       <c r="B494" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C494" s="1" t="s">
         <v>838</v>
@@ -11320,7 +11320,7 @@
         <v>14</v>
       </c>
       <c r="B495" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C495" s="1" t="s">
         <v>839</v>
@@ -11334,7 +11334,7 @@
         <v>14</v>
       </c>
       <c r="B496" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C496" s="1" t="s">
         <v>839</v>
@@ -11348,7 +11348,7 @@
         <v>14</v>
       </c>
       <c r="B497" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C497" s="1" t="s">
         <v>840</v>
@@ -11362,7 +11362,7 @@
         <v>14</v>
       </c>
       <c r="B498" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C498" s="1" t="s">
         <v>841</v>
@@ -11376,7 +11376,7 @@
         <v>14</v>
       </c>
       <c r="B499" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C499" s="1" t="s">
         <v>841</v>
@@ -11390,7 +11390,7 @@
         <v>14</v>
       </c>
       <c r="B500" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C500" s="1" t="s">
         <v>841</v>
@@ -11404,7 +11404,7 @@
         <v>14</v>
       </c>
       <c r="B501" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C501" s="1" t="s">
         <v>842</v>
